--- a/MAPAS EDUCAÇÃO INTEGRAL.xlsx
+++ b/MAPAS EDUCAÇÃO INTEGRAL.xlsx
@@ -19,469 +19,874 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="979" uniqueCount="448">
   <si>
+    <t>EDUCAÇÃO INTEGRAL MUNICÍPIOS 2014</t>
+  </si>
+  <si>
+    <t>EDUCAÇÃO INTEGRAL MUNICÍPIOS 2019</t>
+  </si>
+  <si>
+    <t>EDUCAÇÃO INTEGRAL MUNICÍPIOS 2022</t>
+  </si>
+  <si>
     <t>EDUCAÇÃO INTEGRAL MUNICÍPIOS 8 municipios</t>
   </si>
   <si>
-    <t>EDUCAÇÃO INTEGRAL MUNICÍPIOS 2019</t>
-  </si>
-  <si>
-    <t>EDUCAÇÃO INTEGRAL MUNICÍPIOS 2022</t>
-  </si>
-  <si>
-    <t>EDUCAÇÃO INTEGRAL MUNICÍPIOS 2014</t>
-  </si>
-  <si>
     <t>Item</t>
   </si>
   <si>
     <t>Município</t>
   </si>
   <si>
+    <t>ABAIRA</t>
+  </si>
+  <si>
+    <t>ABARE</t>
+  </si>
+  <si>
+    <t>ADUSTINA</t>
+  </si>
+  <si>
+    <t>AIQUARA</t>
+  </si>
+  <si>
+    <t>ALAGOINHAS</t>
+  </si>
+  <si>
+    <t>ALCOBACA</t>
+  </si>
+  <si>
     <t>GENTIO DO OURO</t>
   </si>
   <si>
+    <t>AMARGOSA</t>
+  </si>
+  <si>
+    <t>ANAGE</t>
+  </si>
+  <si>
+    <t>LAMARAO</t>
+  </si>
+  <si>
+    <t>ANDARAI</t>
+  </si>
+  <si>
+    <t>SERRINHA</t>
+  </si>
+  <si>
+    <t>ANGICAL</t>
+  </si>
+  <si>
+    <t>FIRMINO ALVES</t>
+  </si>
+  <si>
+    <t>ANTONIO GONCALVES</t>
+  </si>
+  <si>
+    <t>CATU</t>
+  </si>
+  <si>
+    <t>APORA</t>
+  </si>
+  <si>
+    <t>APUAREMA</t>
+  </si>
+  <si>
+    <t>FEIRA DE SANTANA</t>
+  </si>
+  <si>
+    <t>ARAMARI</t>
+  </si>
+  <si>
     <t>Barrocas</t>
   </si>
   <si>
+    <t>VITORIA DA CONQUISTA</t>
+  </si>
+  <si>
+    <t>AURELINO LEAL</t>
+  </si>
+  <si>
+    <t>BAIANOPOLIS</t>
+  </si>
+  <si>
+    <t>Canudos</t>
+  </si>
+  <si>
+    <t>SALVADOR</t>
+  </si>
+  <si>
+    <t>BAIXA GRANDE</t>
+  </si>
+  <si>
     <t>BOM JESUS DA LAPA</t>
   </si>
   <si>
-    <t>Canudos</t>
-  </si>
-  <si>
-    <t>ABAIRA</t>
-  </si>
-  <si>
-    <t>LAMARAO</t>
+    <t>João Dourado</t>
+  </si>
+  <si>
+    <t>EUNAPOLIS</t>
+  </si>
+  <si>
+    <t>BARRA</t>
   </si>
   <si>
     <t>PARATINGA</t>
   </si>
   <si>
-    <t>João Dourado</t>
-  </si>
-  <si>
-    <t>SERRINHA</t>
-  </si>
-  <si>
-    <t>ABARE</t>
+    <t>Lajedo do Tabocal</t>
   </si>
   <si>
     <t>BARRA DA ESTIVA</t>
   </si>
   <si>
-    <t>Lajedo do Tabocal</t>
-  </si>
-  <si>
-    <t>FIRMINO ALVES</t>
-  </si>
-  <si>
-    <t>ADUSTINA</t>
-  </si>
-  <si>
-    <t>CATU</t>
-  </si>
-  <si>
-    <t>AIQUARA</t>
-  </si>
-  <si>
-    <t>FEIRA DE SANTANA</t>
-  </si>
-  <si>
-    <t>ALAGOINHAS</t>
+    <t>Maiquinique</t>
+  </si>
+  <si>
+    <t>BARRA DO ROCHA</t>
+  </si>
+  <si>
+    <t>Santa Cruz da Vitória</t>
+  </si>
+  <si>
+    <t>BARREIRAS</t>
+  </si>
+  <si>
+    <t>São Desifério</t>
+  </si>
+  <si>
+    <t>BOA NOVA</t>
   </si>
   <si>
     <t>ILHEUS</t>
   </si>
   <si>
-    <t>VITORIA DA CONQUISTA</t>
-  </si>
-  <si>
-    <t>ALCOBACA</t>
+    <t>Varzedo</t>
   </si>
   <si>
     <t>ITABUNA</t>
   </si>
   <si>
-    <t>ANTONIO GONCALVES</t>
-  </si>
-  <si>
-    <t>AMARGOSA</t>
-  </si>
-  <si>
-    <t>Maiquinique</t>
+    <t>BONINAL</t>
   </si>
   <si>
     <t>ITAMARAJU</t>
   </si>
   <si>
-    <t>SALVADOR</t>
-  </si>
-  <si>
-    <t>ANAGE</t>
+    <t>BONITO</t>
   </si>
   <si>
     <t>NOVA VICOSA</t>
   </si>
   <si>
-    <t>Santa Cruz da Vitória</t>
-  </si>
-  <si>
-    <t>EUNAPOLIS</t>
-  </si>
-  <si>
-    <t>ANDARAI</t>
+    <t>BOQUIRA</t>
   </si>
   <si>
     <t>TEIXEIRA DE FREITAS</t>
   </si>
   <si>
-    <t>São Desifério</t>
-  </si>
-  <si>
-    <t>ANGICAL</t>
-  </si>
-  <si>
-    <t>Varzedo</t>
-  </si>
-  <si>
-    <t>APORA</t>
+    <t>BOTUPORA</t>
+  </si>
+  <si>
+    <t>BREJOLANDIA</t>
+  </si>
+  <si>
+    <t>BROTAS DE MACAUBAS</t>
   </si>
   <si>
     <t>JUAZEIRO</t>
   </si>
   <si>
+    <t>BRUMADO</t>
+  </si>
+  <si>
     <t>SENTO SE</t>
   </si>
   <si>
-    <t>APUAREMA</t>
+    <t>CACULE</t>
   </si>
   <si>
     <t>SOBRADINHO</t>
   </si>
   <si>
-    <t>ARAMARI</t>
+    <t>CAEM</t>
   </si>
   <si>
     <t>CANDIBA</t>
   </si>
   <si>
-    <t>AURELINO LEAL</t>
+    <t>CAETITE</t>
   </si>
   <si>
     <t>RIACHAO DO JACUIPE</t>
   </si>
   <si>
-    <t>BAIANOPOLIS</t>
+    <t>CAIRU</t>
   </si>
   <si>
     <t>CAÉM</t>
   </si>
   <si>
-    <t>BAIXA GRANDE</t>
+    <t>CAMACAN</t>
   </si>
   <si>
     <t>JACOBINA</t>
   </si>
   <si>
-    <t>BARRA</t>
+    <t>CAMACARI</t>
   </si>
   <si>
     <t>MIGUEL CALMON</t>
   </si>
   <si>
+    <t>CAMPO FORMOSO</t>
+  </si>
+  <si>
     <t>CIPÓ</t>
   </si>
   <si>
-    <t>BARRA DO ROCHA</t>
-  </si>
-  <si>
     <t>FÁTIMA</t>
   </si>
   <si>
-    <t>BARREIRAS</t>
-  </si>
-  <si>
-    <t>BOA NOVA</t>
+    <t>CAPELA DO ALTO ALEGRE</t>
+  </si>
+  <si>
+    <t>CAPIM GROSSO</t>
   </si>
   <si>
     <t>CONDE</t>
   </si>
   <si>
+    <t>CARAVELAS</t>
+  </si>
+  <si>
+    <t>CARDEAL DA SILVA</t>
+  </si>
+  <si>
+    <t>CASA NOVA</t>
+  </si>
+  <si>
     <t>SANTO ESTÊVÃO</t>
   </si>
   <si>
-    <t>BONINAL</t>
-  </si>
-  <si>
-    <t>BONITO</t>
+    <t>CATOLANDIA</t>
   </si>
   <si>
     <t>SANTO AMARO</t>
   </si>
   <si>
-    <t>BOQUIRA</t>
-  </si>
-  <si>
-    <t>BOTUPORA</t>
+    <t>CATURAMA</t>
+  </si>
+  <si>
+    <t>CENTRAL</t>
   </si>
   <si>
     <t>IPIAU</t>
   </si>
   <si>
-    <t>BREJOLANDIA</t>
+    <t>CHORROCHO</t>
   </si>
   <si>
     <t>JEQUIE</t>
   </si>
   <si>
+    <t>CIPO</t>
+  </si>
+  <si>
     <t>JITAUNA</t>
   </si>
   <si>
-    <t>BROTAS DE MACAUBAS</t>
+    <t>COCOS</t>
   </si>
   <si>
     <t>PAULO AFONSO</t>
   </si>
   <si>
-    <t>BRUMADO</t>
-  </si>
-  <si>
-    <t>CACULE</t>
+    <t>CONCEICAO DO ALMEIDA</t>
   </si>
   <si>
     <t>SENHOR DO BONFIM</t>
   </si>
   <si>
-    <t>CAEM</t>
+    <t>CORACAO DE MARIA</t>
   </si>
   <si>
     <t>POJUCA</t>
   </si>
   <si>
-    <t>CAETITE</t>
-  </si>
-  <si>
-    <t>CAIRU</t>
-  </si>
-  <si>
-    <t>CAMACAN</t>
+    <t>CORRENTINA</t>
+  </si>
+  <si>
+    <t>COTEGIPE</t>
+  </si>
+  <si>
+    <t>CRAVOLANDIA</t>
   </si>
   <si>
     <t>PORTO SEGURO</t>
   </si>
   <si>
-    <t>CAMACARI</t>
-  </si>
-  <si>
-    <t>CAMPO FORMOSO</t>
-  </si>
-  <si>
-    <t>CAPELA DO ALTO ALEGRE</t>
-  </si>
-  <si>
-    <t>CAPIM GROSSO</t>
-  </si>
-  <si>
-    <t>CARAVELAS</t>
-  </si>
-  <si>
-    <t>CARDEAL DA SILVA</t>
-  </si>
-  <si>
-    <t>CASA NOVA</t>
-  </si>
-  <si>
-    <t>CATOLANDIA</t>
+    <t>CRISOPOLIS</t>
+  </si>
+  <si>
+    <t>CURACA</t>
+  </si>
+  <si>
+    <t>DIAS D AVILA</t>
+  </si>
+  <si>
+    <t>ELISIO MEDRADO</t>
+  </si>
+  <si>
+    <t>ENCRUZILHADA</t>
+  </si>
+  <si>
+    <t>ERICO CARDOSO</t>
+  </si>
+  <si>
+    <t>EUCLIDES DA CUNHA</t>
+  </si>
+  <si>
+    <t>FATIMA</t>
+  </si>
+  <si>
+    <t>FEIRA DA MATA</t>
+  </si>
+  <si>
+    <t>FLORESTA AZUL</t>
+  </si>
+  <si>
+    <t>GLORIA</t>
+  </si>
+  <si>
+    <t>GONGOGI</t>
+  </si>
+  <si>
+    <t>GUANAMBI</t>
+  </si>
+  <si>
+    <t>HELIOPOLIS</t>
+  </si>
+  <si>
+    <t>IACU</t>
+  </si>
+  <si>
+    <t>IBIASSUCE</t>
+  </si>
+  <si>
+    <t>IBICARAI</t>
+  </si>
+  <si>
+    <t>IBIRAPITANGA</t>
+  </si>
+  <si>
+    <t>IBIRATAIA</t>
+  </si>
+  <si>
+    <t>IGAPORA</t>
+  </si>
+  <si>
+    <t>IGRAPIUNA</t>
+  </si>
+  <si>
+    <t>INHAMBUPE</t>
+  </si>
+  <si>
+    <t>IRAQUARA</t>
+  </si>
+  <si>
+    <t>IRARA</t>
+  </si>
+  <si>
+    <t>ITACARE</t>
+  </si>
+  <si>
+    <t>ITAGI</t>
+  </si>
+  <si>
+    <t>ITAGIBA</t>
+  </si>
+  <si>
+    <t>ITAMARI</t>
+  </si>
+  <si>
+    <t>ITANAGRA</t>
+  </si>
+  <si>
+    <t>ITANHEM</t>
+  </si>
+  <si>
+    <t>ITAPEBI</t>
+  </si>
+  <si>
+    <t>ITAPETINGA</t>
+  </si>
+  <si>
+    <t>ITARANTIM</t>
+  </si>
+  <si>
+    <t>ITIUBA</t>
+  </si>
+  <si>
+    <t>ITUBERA</t>
+  </si>
+  <si>
+    <t>JAGUARARI</t>
+  </si>
+  <si>
+    <t>JAGUARIPE</t>
+  </si>
+  <si>
+    <t>JUSSARI</t>
+  </si>
+  <si>
+    <t>LAJEDINHO</t>
+  </si>
+  <si>
+    <t>LAPAO</t>
   </si>
   <si>
     <t>EDUCAÇÃO INTEGRAL MUNICÍPIOS 2023</t>
   </si>
   <si>
+    <t>LICINIO DE ALMEIDA</t>
+  </si>
+  <si>
+    <t>LUIS EDUARDO MAGALHAES</t>
+  </si>
+  <si>
+    <t>MACAUBAS</t>
+  </si>
+  <si>
+    <t>MACURURE</t>
+  </si>
+  <si>
+    <t>MADRE DE DEUS</t>
+  </si>
+  <si>
+    <t>MAIRI</t>
+  </si>
+  <si>
+    <t>MANOEL VITORINO</t>
+  </si>
+  <si>
+    <t>MANSIDAO</t>
+  </si>
+  <si>
+    <t>MARAGOGIPE</t>
+  </si>
+  <si>
+    <t>MARAU</t>
+  </si>
+  <si>
+    <t>MASCOTE</t>
+  </si>
+  <si>
+    <t>MATA DE SAO JOAO</t>
+  </si>
+  <si>
+    <t>MILAGRES</t>
+  </si>
+  <si>
+    <t>MIRANGABA</t>
+  </si>
+  <si>
+    <t>MONTE SANTO</t>
+  </si>
+  <si>
+    <t>ALMADINA</t>
+  </si>
+  <si>
+    <t>MORTUGABA</t>
+  </si>
+  <si>
+    <t>MUCURI</t>
+  </si>
+  <si>
+    <t>MUNDO NOVO</t>
+  </si>
+  <si>
+    <t>AMELIA RODRIGUES</t>
+  </si>
+  <si>
+    <t>MUQUEM DE SAO FRANCISCO</t>
+  </si>
+  <si>
+    <t>MUTUIPE</t>
+  </si>
+  <si>
+    <t>NILO PECANHA</t>
+  </si>
+  <si>
+    <t>NOVA FATIMA</t>
+  </si>
+  <si>
+    <t>ANDORINHA</t>
+  </si>
+  <si>
+    <t>NOVA IBIA</t>
+  </si>
+  <si>
+    <t>NOVA ITARANA</t>
+  </si>
+  <si>
+    <t>ANGUERA</t>
+  </si>
+  <si>
+    <t>OLINDINA</t>
+  </si>
+  <si>
+    <t>ANTAS</t>
+  </si>
+  <si>
+    <t>OURICANGAS</t>
+  </si>
+  <si>
+    <t>OUROLANDIA</t>
+  </si>
+  <si>
+    <t>PALMAS DE MONTE ALTO</t>
+  </si>
+  <si>
+    <t>PARAMIRIM</t>
+  </si>
+  <si>
+    <t>ARACAS</t>
+  </si>
+  <si>
+    <t>PAU BRASIL</t>
+  </si>
+  <si>
+    <t>ARACATU</t>
+  </si>
+  <si>
+    <t>EDUCAÇÃO INTEGRAL MUNICÍPIOS 2026</t>
+  </si>
+  <si>
+    <t>PE DE SERRA</t>
+  </si>
+  <si>
     <t>IPUPIARA</t>
   </si>
   <si>
-    <t>CATURAMA</t>
-  </si>
-  <si>
-    <t>CENTRAL</t>
-  </si>
-  <si>
-    <t>CHORROCHO</t>
-  </si>
-  <si>
-    <t>CIPO</t>
-  </si>
-  <si>
-    <t>COCOS</t>
-  </si>
-  <si>
-    <t>CONCEICAO DO ALMEIDA</t>
+    <t>PINDOBACU</t>
+  </si>
+  <si>
+    <t>ARATACA</t>
+  </si>
+  <si>
+    <t>PINTADAS</t>
+  </si>
+  <si>
+    <t>ARATUIPE</t>
+  </si>
+  <si>
+    <t>POCOES</t>
+  </si>
+  <si>
+    <t>PONTO NOVO</t>
+  </si>
+  <si>
+    <t>PRESIDENTE JANIO QUADROS</t>
+  </si>
+  <si>
+    <t>PRESIDENTE TANCREDO NEVES</t>
+  </si>
+  <si>
+    <t>ACAJUTIBA</t>
+  </si>
+  <si>
+    <t>QUIXABEIRA</t>
+  </si>
+  <si>
+    <t>BARRA DO CHOCA</t>
+  </si>
+  <si>
+    <t>RIACHAO DAS NEVES</t>
+  </si>
+  <si>
+    <t>AGUA FRIA</t>
+  </si>
+  <si>
+    <t>RIACHO DE SANTANA</t>
+  </si>
+  <si>
+    <t>RIBEIRA DO POMBAL</t>
+  </si>
+  <si>
+    <t>RIBEIRAO DO LARGO</t>
+  </si>
+  <si>
+    <t>BOM JESUS DA SERRA</t>
+  </si>
+  <si>
+    <t>RIO DE CONTAS</t>
+  </si>
+  <si>
+    <t>RIO DO ANTONIO</t>
+  </si>
+  <si>
+    <t>RIO REAL</t>
+  </si>
+  <si>
+    <t>AMERICA DOURADA</t>
+  </si>
+  <si>
+    <t>RUY BARBOSA</t>
+  </si>
+  <si>
+    <t>SANTA INES</t>
+  </si>
+  <si>
+    <t>BREJOES</t>
+  </si>
+  <si>
+    <t>SANTANA</t>
+  </si>
+  <si>
+    <t>SANTO ESTEVAO</t>
+  </si>
+  <si>
+    <t>SAO FELIX</t>
+  </si>
+  <si>
+    <t>ANTONIO CARDOSO</t>
+  </si>
+  <si>
+    <t>SAO FELIX DO CORIBE</t>
+  </si>
+  <si>
+    <t>BUERAREMA</t>
+  </si>
+  <si>
+    <t>SAO FRANCISCO DO CONDE</t>
+  </si>
+  <si>
+    <t>SAO JOSE DA VITORIA</t>
+  </si>
+  <si>
+    <t>SAO JOSE DO JACUIPE</t>
   </si>
   <si>
     <t>Previsão para passar a ofertar 2027</t>
   </si>
   <si>
-    <t>CORACAO DE MARIA</t>
-  </si>
-  <si>
-    <t>CORRENTINA</t>
-  </si>
-  <si>
-    <t>ALMADINA</t>
-  </si>
-  <si>
-    <t>COTEGIPE</t>
-  </si>
-  <si>
-    <t>CRAVOLANDIA</t>
+    <t>CAETANOS</t>
+  </si>
+  <si>
+    <t>CAFARNAUM</t>
+  </si>
+  <si>
+    <t>ARACI</t>
+  </si>
+  <si>
+    <t>SAUBARA</t>
+  </si>
+  <si>
+    <t>SAUDE</t>
+  </si>
+  <si>
+    <t>CANAVIEIRAS</t>
+  </si>
+  <si>
+    <t>SEABRA</t>
+  </si>
+  <si>
+    <t>CANDIDO SALES</t>
+  </si>
+  <si>
+    <t>BANZAE</t>
+  </si>
+  <si>
+    <t>SERRA DO RAMALHO</t>
+  </si>
+  <si>
+    <t>SERRA PRETA</t>
   </si>
   <si>
     <t>PALMEIRAS</t>
   </si>
   <si>
-    <t>AMELIA RODRIGUES</t>
-  </si>
-  <si>
-    <t>CRISOPOLIS</t>
+    <t>SERROLANDIA</t>
   </si>
   <si>
     <t>SANTA LUZIA</t>
   </si>
   <si>
-    <t>CURACA</t>
-  </si>
-  <si>
-    <t>DIAS D AVILA</t>
+    <t>BARRA DO MENDES</t>
   </si>
   <si>
     <t>IBIRAPUÃ</t>
   </si>
   <si>
-    <t>ANDORINHA</t>
-  </si>
-  <si>
-    <t>ELISIO MEDRADO</t>
+    <t>SOUTO SOARES</t>
+  </si>
+  <si>
+    <t>TANHACU</t>
+  </si>
+  <si>
+    <t>BARRO PRETO</t>
   </si>
   <si>
     <t>PIRITIBA</t>
   </si>
   <si>
-    <t>ENCRUZILHADA</t>
-  </si>
-  <si>
-    <t>ANGUERA</t>
-  </si>
-  <si>
-    <t>ERICO CARDOSO</t>
+    <t>TANQUE NOVO</t>
+  </si>
+  <si>
+    <t>BELMONTE</t>
   </si>
   <si>
     <t>RAFAEL JAMBEIRO</t>
   </si>
   <si>
-    <t>ANTAS</t>
-  </si>
-  <si>
-    <t>EUCLIDES DA CUNHA</t>
-  </si>
-  <si>
-    <t>FATIMA</t>
-  </si>
-  <si>
-    <t>EDUCAÇÃO INTEGRAL MUNICÍPIOS 2026</t>
-  </si>
-  <si>
-    <t>FEIRA DA MATA</t>
-  </si>
-  <si>
-    <t>ARACAS</t>
-  </si>
-  <si>
-    <t>ARACATU</t>
+    <t>BELO CAMPO</t>
+  </si>
+  <si>
+    <t>TREMEDAL</t>
   </si>
   <si>
     <t>CÍCERO DANTAS</t>
   </si>
   <si>
-    <t>FLORESTA AZUL</t>
+    <t>BIRITINGA</t>
+  </si>
+  <si>
+    <t>UAUA</t>
   </si>
   <si>
     <t>JANDAÍRA</t>
   </si>
   <si>
-    <t>ARATACA</t>
-  </si>
-  <si>
-    <t>GLORIA</t>
-  </si>
-  <si>
-    <t>ARATUIPE</t>
+    <t>UBATA</t>
+  </si>
+  <si>
+    <t>BOA VISTA DO TUPIM</t>
+  </si>
+  <si>
+    <t>UIBAI</t>
   </si>
   <si>
     <t>CABACEIRAS DO PARAGUAÇU</t>
   </si>
   <si>
-    <t>GONGOGI</t>
-  </si>
-  <si>
-    <t>GUANAMBI</t>
-  </si>
-  <si>
-    <t>HELIOPOLIS</t>
-  </si>
-  <si>
-    <t>ACAJUTIBA</t>
+    <t>UMBURANAS</t>
+  </si>
+  <si>
+    <t>URANDI</t>
+  </si>
+  <si>
+    <t>VALENTE</t>
+  </si>
+  <si>
+    <t>VARZEA DA ROCA</t>
   </si>
   <si>
     <t>SÃO FELIPE</t>
   </si>
   <si>
-    <t>IACU</t>
-  </si>
-  <si>
-    <t>IBIASSUCE</t>
-  </si>
-  <si>
-    <t>AGUA FRIA</t>
-  </si>
-  <si>
-    <t>IBICARAI</t>
+    <t>VERA CRUZ</t>
+  </si>
+  <si>
+    <t>VEREDA</t>
+  </si>
+  <si>
+    <t>WAGNER</t>
+  </si>
+  <si>
+    <t>WANDERLEY</t>
+  </si>
+  <si>
+    <t>COARACI</t>
+  </si>
+  <si>
+    <t>BURITIRAMA</t>
+  </si>
+  <si>
+    <t>CACHOEIRA</t>
+  </si>
+  <si>
+    <t>CONDEUBA</t>
   </si>
   <si>
     <t>SANTA MARIA DA VITÓRIA</t>
   </si>
   <si>
-    <t>IBIRAPITANGA</t>
+    <t>CALDEIRAO GRANDE</t>
+  </si>
+  <si>
+    <t>DARIO MEIRA</t>
   </si>
   <si>
     <t>ITAGIMIRIM</t>
   </si>
   <si>
-    <t>IBIRATAIA</t>
-  </si>
-  <si>
-    <t>BARRA DO CHOCA</t>
-  </si>
-  <si>
-    <t>IGAPORA</t>
+    <t>ITAPICURU</t>
+  </si>
+  <si>
+    <t>CAMAMU</t>
+  </si>
+  <si>
+    <t>DOM BASILIO</t>
+  </si>
+  <si>
+    <t>Proposta para passar a ofertar 2032</t>
+  </si>
+  <si>
+    <t>CAMPO ALEGRE DE LOURDES</t>
+  </si>
+  <si>
+    <t>TABOCAS DO BREJO VELHO</t>
+  </si>
+  <si>
+    <t>Proposta para passar a ofertar 2033</t>
+  </si>
+  <si>
+    <t>CANAPOLIS</t>
+  </si>
+  <si>
+    <t>ENTRE RIOS</t>
+  </si>
+  <si>
+    <t>CANARANA</t>
   </si>
   <si>
     <t>BARRO ALTO</t>
   </si>
   <si>
-    <t>IGRAPIUNA</t>
-  </si>
-  <si>
-    <t>INHAMBUPE</t>
+    <t>CANDEAL</t>
+  </si>
+  <si>
+    <t>CANDEIAS</t>
+  </si>
+  <si>
+    <t>CANSANCAO</t>
+  </si>
+  <si>
+    <t>CARAIBAS</t>
+  </si>
+  <si>
+    <t>CARINHANHA</t>
+  </si>
+  <si>
+    <t>CASTRO ALVES</t>
   </si>
   <si>
     <t>Proposta para passar a ofertar 2027</t>
   </si>
   <si>
-    <t>AMERICA DOURADA</t>
-  </si>
-  <si>
-    <t>BOM JESUS DA SERRA</t>
+    <t>IBIPEBA</t>
+  </si>
+  <si>
+    <t>IBOTIRAMA</t>
+  </si>
+  <si>
+    <t>CONCEICAO DA FEIRA</t>
+  </si>
+  <si>
+    <t>CONCEICAO DO COITE</t>
+  </si>
+  <si>
+    <t>CONCEICAO DO JACUIPE</t>
   </si>
   <si>
     <t>MULUNGU DO MORRO</t>
@@ -490,55 +895,43 @@
     <t>Proposta para passar a ofertar 2028</t>
   </si>
   <si>
+    <t>IPECAETA</t>
+  </si>
+  <si>
     <t>LAJEDÃO</t>
   </si>
   <si>
+    <t>CONTENDAS DO SINCORA</t>
+  </si>
+  <si>
     <t>Proposta para passar a ofertar 2029</t>
   </si>
   <si>
-    <t>IRAQUARA</t>
-  </si>
-  <si>
     <t>CAATIBA</t>
   </si>
   <si>
     <t>Proposta para passar a ofertar 2030</t>
   </si>
   <si>
-    <t>IRARA</t>
+    <t>CORDEIROS</t>
   </si>
   <si>
     <t>RIBEIRA DO AMPARO</t>
   </si>
   <si>
+    <t>IRECE</t>
+  </si>
+  <si>
+    <t>CORIBE</t>
+  </si>
+  <si>
     <t>Proposta para passar a ofertar 2031</t>
   </si>
   <si>
-    <t>ITACARE</t>
-  </si>
-  <si>
-    <t>ITAPICURU</t>
-  </si>
-  <si>
-    <t>BREJOES</t>
-  </si>
-  <si>
-    <t>Proposta para passar a ofertar 2032</t>
-  </si>
-  <si>
-    <t>ITAGI</t>
-  </si>
-  <si>
-    <t>TABOCAS DO BREJO VELHO</t>
-  </si>
-  <si>
-    <t>ITAGIBA</t>
-  </si>
-  <si>
-    <t>Proposta para passar a ofertar 2033</t>
-  </si>
-  <si>
-    <t>ANTONIO CARDOSO</t>
+    <t>ITABERABA</t>
+  </si>
+  <si>
+    <t>CORONEL JOAO SA</t>
   </si>
   <si>
     <t>GUARATINGA</t>
@@ -547,498 +940,105 @@
     <t>Proposta para passar a ofertar 2034</t>
   </si>
   <si>
-    <t>ITAMARI</t>
-  </si>
-  <si>
     <t>ITABELA</t>
   </si>
   <si>
     <t>Proposta para passar a ofertar 2035</t>
   </si>
   <si>
-    <t>BUERAREMA</t>
-  </si>
-  <si>
-    <t>ITANAGRA</t>
-  </si>
-  <si>
     <t>JOÃO DOURADO</t>
   </si>
   <si>
-    <t>ITANHEM</t>
-  </si>
-  <si>
-    <t>ITAPEBI</t>
-  </si>
-  <si>
-    <t>CAETANOS</t>
-  </si>
-  <si>
-    <t>ITAPETINGA</t>
+    <t>CRISTOPOLIS</t>
+  </si>
+  <si>
+    <t>ITAJU DO COLONIA</t>
+  </si>
+  <si>
+    <t>CRUZ DAS ALMAS</t>
+  </si>
+  <si>
+    <t>ITAJUIPE</t>
+  </si>
+  <si>
+    <t>DOM MACEDO COSTA</t>
+  </si>
+  <si>
+    <t>ITAPARICA</t>
+  </si>
+  <si>
+    <t>ITAPE</t>
+  </si>
+  <si>
+    <t>ESPLANADA</t>
+  </si>
+  <si>
+    <t>ITUACU</t>
+  </si>
+  <si>
+    <t>JAGUAQUARA</t>
   </si>
   <si>
     <t>Necessita licitação</t>
   </si>
   <si>
-    <t>ITARANTIM</t>
-  </si>
-  <si>
-    <t>CAFARNAUM</t>
-  </si>
-  <si>
-    <t>ITIUBA</t>
+    <t>FILADELFIA</t>
+  </si>
+  <si>
+    <t>JEREMOABO</t>
+  </si>
+  <si>
+    <t>JIQUIRICA</t>
+  </si>
+  <si>
+    <t>FORMOSA DO RIO PRETO</t>
+  </si>
+  <si>
+    <t>GANDU</t>
+  </si>
+  <si>
+    <t>GAVIAO</t>
+  </si>
+  <si>
+    <t>JUCURUCU</t>
+  </si>
+  <si>
+    <t>JUSSARA</t>
   </si>
   <si>
     <t>BARROCAS</t>
   </si>
   <si>
-    <t>ARACI</t>
-  </si>
-  <si>
-    <t>ITUBERA</t>
-  </si>
-  <si>
-    <t>JAGUARARI</t>
-  </si>
-  <si>
-    <t>JAGUARIPE</t>
+    <t>GOVERNADOR MANGABEIRA</t>
+  </si>
+  <si>
+    <t>GUAJERU</t>
   </si>
   <si>
     <t>MAIQUINIQUE</t>
   </si>
   <si>
-    <t>CANAVIEIRAS</t>
-  </si>
-  <si>
     <t>SANTA CRUZ DA VITÓRIA</t>
   </si>
   <si>
-    <t>CANDIDO SALES</t>
-  </si>
-  <si>
-    <t>JUSSARI</t>
+    <t>MACAJUBA</t>
   </si>
   <si>
     <t>LAJEDO DO TABOCAL</t>
   </si>
   <si>
-    <t>LAJEDINHO</t>
-  </si>
-  <si>
     <t>CANUDOS</t>
   </si>
   <si>
-    <t>BANZAE</t>
-  </si>
-  <si>
-    <t>LAPAO</t>
-  </si>
-  <si>
     <t>SÃO DESIDÉRIO</t>
   </si>
   <si>
-    <t>LICINIO DE ALMEIDA</t>
-  </si>
-  <si>
-    <t>LUIS EDUARDO MAGALHAES</t>
+    <t>IBICOARA</t>
   </si>
   <si>
     <t>VARZEDO</t>
   </si>
   <si>
-    <t>MACAUBAS</t>
-  </si>
-  <si>
-    <t>BARRA DO MENDES</t>
-  </si>
-  <si>
-    <t>MACURURE</t>
-  </si>
-  <si>
-    <t>MADRE DE DEUS</t>
-  </si>
-  <si>
-    <t>MAIRI</t>
-  </si>
-  <si>
-    <t>BARRO PRETO</t>
-  </si>
-  <si>
-    <t>MANOEL VITORINO</t>
-  </si>
-  <si>
-    <t>BELMONTE</t>
-  </si>
-  <si>
-    <t>MANSIDAO</t>
-  </si>
-  <si>
-    <t>COARACI</t>
-  </si>
-  <si>
-    <t>BELO CAMPO</t>
-  </si>
-  <si>
-    <t>MARAGOGIPE</t>
-  </si>
-  <si>
-    <t>BIRITINGA</t>
-  </si>
-  <si>
-    <t>MARAU</t>
-  </si>
-  <si>
-    <t>MASCOTE</t>
-  </si>
-  <si>
-    <t>BOA VISTA DO TUPIM</t>
-  </si>
-  <si>
-    <t>MATA DE SAO JOAO</t>
-  </si>
-  <si>
-    <t>CONDEUBA</t>
-  </si>
-  <si>
-    <t>MILAGRES</t>
-  </si>
-  <si>
-    <t>MIRANGABA</t>
-  </si>
-  <si>
-    <t>MONTE SANTO</t>
-  </si>
-  <si>
-    <t>MORTUGABA</t>
-  </si>
-  <si>
-    <t>MUCURI</t>
-  </si>
-  <si>
-    <t>MUNDO NOVO</t>
-  </si>
-  <si>
-    <t>MUQUEM DE SAO FRANCISCO</t>
-  </si>
-  <si>
-    <t>DARIO MEIRA</t>
-  </si>
-  <si>
-    <t>MUTUIPE</t>
-  </si>
-  <si>
-    <t>NILO PECANHA</t>
-  </si>
-  <si>
-    <t>NOVA FATIMA</t>
-  </si>
-  <si>
-    <t>BURITIRAMA</t>
-  </si>
-  <si>
-    <t>NOVA IBIA</t>
-  </si>
-  <si>
-    <t>CACHOEIRA</t>
-  </si>
-  <si>
-    <t>DOM BASILIO</t>
-  </si>
-  <si>
-    <t>NOVA ITARANA</t>
-  </si>
-  <si>
-    <t>OLINDINA</t>
-  </si>
-  <si>
-    <t>OURICANGAS</t>
-  </si>
-  <si>
-    <t>ENTRE RIOS</t>
-  </si>
-  <si>
-    <t>OUROLANDIA</t>
-  </si>
-  <si>
-    <t>PALMAS DE MONTE ALTO</t>
-  </si>
-  <si>
-    <t>PARAMIRIM</t>
-  </si>
-  <si>
-    <t>CALDEIRAO GRANDE</t>
-  </si>
-  <si>
-    <t>PAU BRASIL</t>
-  </si>
-  <si>
-    <t>CAMAMU</t>
-  </si>
-  <si>
-    <t>PE DE SERRA</t>
-  </si>
-  <si>
-    <t>CAMPO ALEGRE DE LOURDES</t>
-  </si>
-  <si>
-    <t>PINDOBACU</t>
-  </si>
-  <si>
-    <t>PINTADAS</t>
-  </si>
-  <si>
-    <t>CANAPOLIS</t>
-  </si>
-  <si>
-    <t>POCOES</t>
-  </si>
-  <si>
-    <t>CANARANA</t>
-  </si>
-  <si>
-    <t>PONTO NOVO</t>
-  </si>
-  <si>
-    <t>CANDEAL</t>
-  </si>
-  <si>
-    <t>PRESIDENTE JANIO QUADROS</t>
-  </si>
-  <si>
-    <t>CANDEIAS</t>
-  </si>
-  <si>
-    <t>PRESIDENTE TANCREDO NEVES</t>
-  </si>
-  <si>
-    <t>QUIXABEIRA</t>
-  </si>
-  <si>
-    <t>RIACHAO DAS NEVES</t>
-  </si>
-  <si>
-    <t>IBIPEBA</t>
-  </si>
-  <si>
-    <t>CANSANCAO</t>
-  </si>
-  <si>
-    <t>RIACHO DE SANTANA</t>
-  </si>
-  <si>
-    <t>RIBEIRA DO POMBAL</t>
-  </si>
-  <si>
-    <t>IBOTIRAMA</t>
-  </si>
-  <si>
-    <t>RIBEIRAO DO LARGO</t>
-  </si>
-  <si>
-    <t>CARAIBAS</t>
-  </si>
-  <si>
-    <t>RIO DE CONTAS</t>
-  </si>
-  <si>
-    <t>RIO DO ANTONIO</t>
-  </si>
-  <si>
-    <t>RIO REAL</t>
-  </si>
-  <si>
-    <t>CARINHANHA</t>
-  </si>
-  <si>
-    <t>RUY BARBOSA</t>
-  </si>
-  <si>
-    <t>IPECAETA</t>
-  </si>
-  <si>
-    <t>CASTRO ALVES</t>
-  </si>
-  <si>
-    <t>SANTA INES</t>
-  </si>
-  <si>
-    <t>SANTANA</t>
-  </si>
-  <si>
-    <t>SANTO ESTEVAO</t>
-  </si>
-  <si>
-    <t>IRECE</t>
-  </si>
-  <si>
-    <t>SAO FELIX</t>
-  </si>
-  <si>
-    <t>ITABERABA</t>
-  </si>
-  <si>
-    <t>SAO FELIX DO CORIBE</t>
-  </si>
-  <si>
-    <t>SAO FRANCISCO DO CONDE</t>
-  </si>
-  <si>
-    <t>SAO JOSE DA VITORIA</t>
-  </si>
-  <si>
-    <t>CONCEICAO DA FEIRA</t>
-  </si>
-  <si>
-    <t>SAO JOSE DO JACUIPE</t>
-  </si>
-  <si>
-    <t>SAUBARA</t>
-  </si>
-  <si>
-    <t>CONCEICAO DO COITE</t>
-  </si>
-  <si>
-    <t>SAUDE</t>
-  </si>
-  <si>
-    <t>CONCEICAO DO JACUIPE</t>
-  </si>
-  <si>
-    <t>SEABRA</t>
-  </si>
-  <si>
-    <t>ITAJU DO COLONIA</t>
-  </si>
-  <si>
-    <t>ITAJUIPE</t>
-  </si>
-  <si>
-    <t>CONTENDAS DO SINCORA</t>
-  </si>
-  <si>
-    <t>SERRA DO RAMALHO</t>
-  </si>
-  <si>
-    <t>SERRA PRETA</t>
-  </si>
-  <si>
-    <t>CORDEIROS</t>
-  </si>
-  <si>
-    <t>CORIBE</t>
-  </si>
-  <si>
-    <t>SERROLANDIA</t>
-  </si>
-  <si>
-    <t>CORONEL JOAO SA</t>
-  </si>
-  <si>
-    <t>SOUTO SOARES</t>
-  </si>
-  <si>
-    <t>ITAPARICA</t>
-  </si>
-  <si>
-    <t>TANHACU</t>
-  </si>
-  <si>
-    <t>TANQUE NOVO</t>
-  </si>
-  <si>
-    <t>ITAPE</t>
-  </si>
-  <si>
-    <t>CRISTOPOLIS</t>
-  </si>
-  <si>
-    <t>TREMEDAL</t>
-  </si>
-  <si>
-    <t>CRUZ DAS ALMAS</t>
-  </si>
-  <si>
-    <t>UAUA</t>
-  </si>
-  <si>
-    <t>UBATA</t>
-  </si>
-  <si>
-    <t>UIBAI</t>
-  </si>
-  <si>
-    <t>UMBURANAS</t>
-  </si>
-  <si>
-    <t>DOM MACEDO COSTA</t>
-  </si>
-  <si>
-    <t>URANDI</t>
-  </si>
-  <si>
-    <t>ITUACU</t>
-  </si>
-  <si>
-    <t>VALENTE</t>
-  </si>
-  <si>
-    <t>VARZEA DA ROCA</t>
-  </si>
-  <si>
-    <t>VERA CRUZ</t>
-  </si>
-  <si>
-    <t>VEREDA</t>
-  </si>
-  <si>
-    <t>ESPLANADA</t>
-  </si>
-  <si>
-    <t>WAGNER</t>
-  </si>
-  <si>
-    <t>WANDERLEY</t>
-  </si>
-  <si>
-    <t>JAGUAQUARA</t>
-  </si>
-  <si>
-    <t>FILADELFIA</t>
-  </si>
-  <si>
-    <t>JEREMOABO</t>
-  </si>
-  <si>
-    <t>JIQUIRICA</t>
-  </si>
-  <si>
-    <t>FORMOSA DO RIO PRETO</t>
-  </si>
-  <si>
-    <t>GANDU</t>
-  </si>
-  <si>
-    <t>GAVIAO</t>
-  </si>
-  <si>
-    <t>JUCURUCU</t>
-  </si>
-  <si>
-    <t>JUSSARA</t>
-  </si>
-  <si>
-    <t>GOVERNADOR MANGABEIRA</t>
-  </si>
-  <si>
-    <t>GUAJERU</t>
-  </si>
-  <si>
-    <t>MACAJUBA</t>
-  </si>
-  <si>
-    <t>IBICOARA</t>
-  </si>
-  <si>
     <t>IBICUI</t>
   </si>
   <si>
@@ -1048,15 +1048,15 @@
     <t>IBIQUERA</t>
   </si>
   <si>
+    <t>MATINA</t>
+  </si>
+  <si>
     <t>IBITIARA</t>
   </si>
   <si>
     <t>IBITITA</t>
   </si>
   <si>
-    <t>MATINA</t>
-  </si>
-  <si>
     <t>ICHU</t>
   </si>
   <si>
@@ -1078,45 +1078,45 @@
     <t>OLIVEIRA DOS BREJINHOS</t>
   </si>
   <si>
+    <t>ITAETE</t>
+  </si>
+  <si>
+    <t>ITAGUACU DA BAHIA</t>
+  </si>
+  <si>
     <t>PEDRAO</t>
   </si>
   <si>
-    <t>ITAETE</t>
-  </si>
-  <si>
     <t>PINDAI</t>
   </si>
   <si>
+    <t>ITAMBE</t>
+  </si>
+  <si>
     <t>PLANALTO</t>
   </si>
   <si>
-    <t>ITAGUACU DA BAHIA</t>
-  </si>
-  <si>
-    <t>ITAMBE</t>
-  </si>
-  <si>
     <t>PRESIDENTE DUTRA</t>
   </si>
   <si>
     <t>ITAPITANGA</t>
   </si>
   <si>
+    <t>REMANSO</t>
+  </si>
+  <si>
     <t>ITAQUARA</t>
   </si>
   <si>
+    <t>RETIROLANDIA</t>
+  </si>
+  <si>
     <t>ITATIM</t>
   </si>
   <si>
     <t>ITIRUCU</t>
   </si>
   <si>
-    <t>REMANSO</t>
-  </si>
-  <si>
-    <t>RETIROLANDIA</t>
-  </si>
-  <si>
     <t>ITORORO</t>
   </si>
   <si>
@@ -1165,58 +1165,58 @@
     <t>MACARANI</t>
   </si>
   <si>
+    <t>SITIO DO QUINTO</t>
+  </si>
+  <si>
     <t>MAETINGA</t>
   </si>
   <si>
     <t>MALHADA</t>
   </si>
   <si>
+    <t>TANQUINHO</t>
+  </si>
+  <si>
     <t>MALHADA DE PEDRAS</t>
   </si>
   <si>
-    <t>SITIO DO QUINTO</t>
+    <t>TAPEROA</t>
+  </si>
+  <si>
+    <t>TEOLANDIA</t>
   </si>
   <si>
     <t>MARACAS</t>
   </si>
   <si>
-    <t>TANQUINHO</t>
+    <t>TUCANO</t>
   </si>
   <si>
     <t>MARCIONILIO SOUZA</t>
   </si>
   <si>
-    <t>TAPEROA</t>
-  </si>
-  <si>
-    <t>TEOLANDIA</t>
+    <t>UBAITABA</t>
   </si>
   <si>
     <t>MEDEIROS NETO</t>
   </si>
   <si>
-    <t>TUCANO</t>
-  </si>
-  <si>
-    <t>UBAITABA</t>
+    <t>URUCUCA</t>
   </si>
   <si>
     <t>MIRANTE</t>
   </si>
   <si>
+    <t>VARZEA NOVA</t>
+  </si>
+  <si>
     <t>MORPARA</t>
   </si>
   <si>
     <t>MORRO DO CHAPEU</t>
   </si>
   <si>
-    <t>URUCUCA</t>
-  </si>
-  <si>
     <t>MUCUGE</t>
-  </si>
-  <si>
-    <t>VARZEA NOVA</t>
   </si>
   <si>
     <t>MUNIZ FERREIRA</t>
@@ -1367,7 +1367,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="5">
+  <fonts count="7">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -1393,6 +1393,19 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11.0"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11.0"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -1407,8 +1420,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor theme="6"/>
+        <fgColor rgb="FFFF9900"/>
+        <bgColor rgb="FFFF9900"/>
       </patternFill>
     </fill>
     <fill>
@@ -1444,7 +1457,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1457,25 +1470,31 @@
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="2" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="2" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="4" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="4" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
   </cellXfs>
@@ -1724,7 +1743,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2">
@@ -1740,7 +1759,7 @@
         <v>1.0</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4">
@@ -1748,7 +1767,7 @@
         <v>2.0</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5">
@@ -1756,7 +1775,7 @@
         <v>3.0</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6">
@@ -1764,7 +1783,7 @@
         <v>4.0</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7">
@@ -1772,7 +1791,7 @@
         <v>5.0</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8">
@@ -1780,7 +1799,7 @@
         <v>6.0</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9">
@@ -1788,7 +1807,7 @@
         <v>7.0</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10">
@@ -1796,7 +1815,7 @@
         <v>8.0</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11">
@@ -1804,7 +1823,7 @@
         <v>9.0</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12">
@@ -1812,7 +1831,7 @@
         <v>10.0</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13">
@@ -1871,7 +1890,7 @@
         <v>1.0</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4">
@@ -1879,7 +1898,7 @@
         <v>2.0</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5">
@@ -1887,7 +1906,7 @@
         <v>3.0</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>12</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6">
@@ -1895,7 +1914,7 @@
         <v>4.0</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>16</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7">
@@ -1903,7 +1922,7 @@
         <v>5.0</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8">
@@ -1911,7 +1930,7 @@
         <v>6.0</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9">
@@ -1919,7 +1938,7 @@
         <v>7.0</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
     </row>
     <row r="10">
@@ -1927,7 +1946,7 @@
         <v>8.0</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>27</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11">
@@ -1935,7 +1954,7 @@
         <v>9.0</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12">
@@ -1943,7 +1962,7 @@
         <v>10.0</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>34</v>
+        <v>52</v>
       </c>
     </row>
     <row r="13">
@@ -1951,7 +1970,7 @@
         <v>11.0</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
     </row>
     <row r="14">
@@ -1959,7 +1978,7 @@
         <v>12.0</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15">
@@ -1967,7 +1986,7 @@
         <v>13.0</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16">
@@ -1975,7 +1994,7 @@
         <v>14.0</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
     </row>
     <row r="17">
@@ -1983,7 +2002,7 @@
         <v>15.0</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
     </row>
     <row r="18">
@@ -1991,7 +2010,7 @@
         <v>16.0</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>46</v>
+        <v>62</v>
       </c>
     </row>
     <row r="19">
@@ -1999,7 +2018,7 @@
         <v>17.0</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>48</v>
+        <v>64</v>
       </c>
     </row>
     <row r="20">
@@ -2007,7 +2026,7 @@
         <v>18.0</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
     </row>
     <row r="21">
@@ -2015,7 +2034,7 @@
         <v>19.0</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
     </row>
     <row r="22">
@@ -2023,7 +2042,7 @@
         <v>20.0</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>54</v>
+        <v>70</v>
       </c>
     </row>
     <row r="23">
@@ -2031,7 +2050,7 @@
         <v>21.0</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
     </row>
     <row r="24">
@@ -2039,7 +2058,7 @@
         <v>22.0</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
     </row>
     <row r="25">
@@ -2047,7 +2066,7 @@
         <v>23.0</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>59</v>
+        <v>75</v>
       </c>
     </row>
     <row r="26">
@@ -2055,7 +2074,7 @@
         <v>24.0</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27">
@@ -2063,7 +2082,7 @@
         <v>25.0</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>62</v>
+        <v>78</v>
       </c>
     </row>
     <row r="28">
@@ -2071,7 +2090,7 @@
         <v>26.0</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="29">
@@ -2079,7 +2098,7 @@
         <v>27.0</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
     </row>
     <row r="30">
@@ -2087,7 +2106,7 @@
         <v>28.0</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="31">
@@ -2095,7 +2114,7 @@
         <v>29.0</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
     </row>
     <row r="32">
@@ -2103,7 +2122,7 @@
         <v>30.0</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="33">
@@ -2111,7 +2130,7 @@
         <v>31.0</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
     </row>
     <row r="34">
@@ -2119,7 +2138,7 @@
         <v>32.0</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
     </row>
     <row r="35">
@@ -2127,7 +2146,7 @@
         <v>33.0</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>72</v>
+        <v>91</v>
       </c>
     </row>
     <row r="36">
@@ -2135,7 +2154,7 @@
         <v>34.0</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>74</v>
+        <v>93</v>
       </c>
     </row>
     <row r="37">
@@ -2143,7 +2162,7 @@
         <v>35.0</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
     </row>
     <row r="38">
@@ -2151,7 +2170,7 @@
         <v>36.0</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
     </row>
     <row r="39">
@@ -2159,7 +2178,7 @@
         <v>37.0</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>79</v>
+        <v>97</v>
       </c>
     </row>
     <row r="40">
@@ -2167,7 +2186,7 @@
         <v>38.0</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="41">
@@ -2175,7 +2194,7 @@
         <v>39.0</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="42">
@@ -2183,7 +2202,7 @@
         <v>40.0</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>83</v>
+        <v>101</v>
       </c>
     </row>
     <row r="43">
@@ -2258,7 +2277,7 @@
         <v>1.0</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
@@ -2266,7 +2285,7 @@
         <v>2.0</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
@@ -2274,7 +2293,7 @@
         <v>3.0</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
@@ -2282,7 +2301,7 @@
         <v>4.0</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7">
@@ -2290,7 +2309,7 @@
         <v>5.0</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
@@ -2298,7 +2317,7 @@
         <v>6.0</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9">
@@ -2306,7 +2325,7 @@
         <v>7.0</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10">
@@ -2314,7 +2333,7 @@
         <v>8.0</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11">
@@ -2322,7 +2341,7 @@
         <v>9.0</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12">
@@ -2330,7 +2349,7 @@
         <v>10.0</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13">
@@ -2338,7 +2357,7 @@
         <v>11.0</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14">
@@ -2346,7 +2365,7 @@
         <v>12.0</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15">
@@ -2354,7 +2373,7 @@
         <v>13.0</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>45</v>
+        <v>23</v>
       </c>
     </row>
     <row r="16">
@@ -2362,7 +2381,7 @@
         <v>14.0</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
     </row>
     <row r="17">
@@ -2370,7 +2389,7 @@
         <v>15.0</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>49</v>
+        <v>28</v>
       </c>
     </row>
     <row r="18">
@@ -2378,7 +2397,7 @@
         <v>16.0</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>51</v>
+        <v>29</v>
       </c>
     </row>
     <row r="19">
@@ -2386,7 +2405,7 @@
         <v>17.0</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>53</v>
+        <v>32</v>
       </c>
     </row>
     <row r="20">
@@ -2394,7 +2413,7 @@
         <v>18.0</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>55</v>
+        <v>36</v>
       </c>
     </row>
     <row r="21">
@@ -2402,7 +2421,7 @@
         <v>19.0</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>16</v>
+        <v>39</v>
       </c>
     </row>
     <row r="22">
@@ -2410,7 +2429,7 @@
         <v>20.0</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>58</v>
+        <v>41</v>
       </c>
     </row>
     <row r="23">
@@ -2418,7 +2437,7 @@
         <v>21.0</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>60</v>
+        <v>43</v>
       </c>
     </row>
     <row r="24">
@@ -2426,7 +2445,7 @@
         <v>22.0</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
     </row>
     <row r="25">
@@ -2434,7 +2453,7 @@
         <v>23.0</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
     </row>
     <row r="26">
@@ -2442,7 +2461,7 @@
         <v>24.0</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
     </row>
     <row r="27">
@@ -2450,7 +2469,7 @@
         <v>25.0</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
     </row>
     <row r="28">
@@ -2458,7 +2477,7 @@
         <v>26.0</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>67</v>
+        <v>53</v>
       </c>
     </row>
     <row r="29">
@@ -2466,7 +2485,7 @@
         <v>27.0</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
     </row>
     <row r="30">
@@ -2474,7 +2493,7 @@
         <v>28.0</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>70</v>
+        <v>56</v>
       </c>
     </row>
     <row r="31">
@@ -2482,7 +2501,7 @@
         <v>29.0</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>73</v>
+        <v>57</v>
       </c>
     </row>
     <row r="32">
@@ -2490,7 +2509,7 @@
         <v>30.0</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
     </row>
     <row r="33">
@@ -2498,7 +2517,7 @@
         <v>31.0</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
     </row>
     <row r="34">
@@ -2506,7 +2525,7 @@
         <v>32.0</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>78</v>
+        <v>63</v>
       </c>
     </row>
     <row r="35">
@@ -2514,7 +2533,7 @@
         <v>33.0</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
     </row>
     <row r="36">
@@ -2522,7 +2541,7 @@
         <v>34.0</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
     </row>
     <row r="37">
@@ -2530,7 +2549,7 @@
         <v>35.0</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
     </row>
     <row r="38">
@@ -2538,7 +2557,7 @@
         <v>36.0</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
     </row>
     <row r="39">
@@ -2546,7 +2565,7 @@
         <v>37.0</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
     </row>
     <row r="40">
@@ -2554,7 +2573,7 @@
         <v>38.0</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>48</v>
+        <v>64</v>
       </c>
     </row>
     <row r="41">
@@ -2562,7 +2581,7 @@
         <v>39.0</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
     </row>
     <row r="42">
@@ -2570,7 +2589,7 @@
         <v>40.0</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
     </row>
     <row r="43">
@@ -2578,7 +2597,7 @@
         <v>41.0</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
     </row>
     <row r="44">
@@ -2586,7 +2605,7 @@
         <v>42.0</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
     </row>
     <row r="45">
@@ -2594,7 +2613,7 @@
         <v>43.0</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
     </row>
     <row r="46">
@@ -2602,7 +2621,7 @@
         <v>44.0</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
     </row>
     <row r="47">
@@ -2610,7 +2629,7 @@
         <v>45.0</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="48">
@@ -2618,7 +2637,7 @@
         <v>46.0</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
     </row>
     <row r="49">
@@ -2626,7 +2645,7 @@
         <v>47.0</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
     </row>
     <row r="50">
@@ -2634,7 +2653,7 @@
         <v>48.0</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
     </row>
     <row r="51">
@@ -2642,7 +2661,7 @@
         <v>49.0</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
     </row>
     <row r="52">
@@ -2650,7 +2669,7 @@
         <v>50.0</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
     </row>
     <row r="53">
@@ -2658,7 +2677,7 @@
         <v>51.0</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
     </row>
     <row r="54">
@@ -2666,7 +2685,7 @@
         <v>52.0</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>62</v>
+        <v>78</v>
       </c>
     </row>
     <row r="55">
@@ -2674,7 +2693,7 @@
         <v>53.0</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
     </row>
     <row r="56">
@@ -2682,7 +2701,7 @@
         <v>54.0</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
     </row>
     <row r="57">
@@ -2690,7 +2709,7 @@
         <v>55.0</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
     </row>
     <row r="58">
@@ -2698,7 +2717,7 @@
         <v>56.0</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
     </row>
     <row r="59">
@@ -2706,7 +2725,7 @@
         <v>57.0</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
     </row>
     <row r="60">
@@ -2714,7 +2733,7 @@
         <v>58.0</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
     </row>
     <row r="61">
@@ -2722,7 +2741,7 @@
         <v>59.0</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
     </row>
     <row r="62">
@@ -2730,7 +2749,7 @@
         <v>60.0</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
     </row>
     <row r="63">
@@ -2738,7 +2757,7 @@
         <v>61.0</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
     </row>
     <row r="64">
@@ -2746,7 +2765,7 @@
         <v>62.0</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
     </row>
     <row r="65">
@@ -2754,7 +2773,7 @@
         <v>63.0</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
     </row>
     <row r="66">
@@ -2762,7 +2781,7 @@
         <v>64.0</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="67">
@@ -2770,7 +2789,7 @@
         <v>65.0</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
     </row>
     <row r="68">
@@ -2778,7 +2797,7 @@
         <v>66.0</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>124</v>
+        <v>110</v>
       </c>
     </row>
     <row r="69">
@@ -2786,7 +2805,7 @@
         <v>67.0</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="70">
@@ -2794,7 +2813,7 @@
         <v>68.0</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="71">
@@ -2802,7 +2821,7 @@
         <v>69.0</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>128</v>
+        <v>111</v>
       </c>
     </row>
     <row r="72">
@@ -2810,7 +2829,7 @@
         <v>70.0</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="73">
@@ -2818,7 +2837,7 @@
         <v>71.0</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>131</v>
+        <v>112</v>
       </c>
     </row>
     <row r="74">
@@ -2826,7 +2845,7 @@
         <v>72.0</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>134</v>
+        <v>113</v>
       </c>
     </row>
     <row r="75">
@@ -2834,7 +2853,7 @@
         <v>73.0</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>135</v>
+        <v>114</v>
       </c>
     </row>
     <row r="76">
@@ -2842,7 +2861,7 @@
         <v>74.0</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>136</v>
+        <v>115</v>
       </c>
     </row>
     <row r="77">
@@ -2850,7 +2869,7 @@
         <v>75.0</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>139</v>
+        <v>116</v>
       </c>
     </row>
     <row r="78">
@@ -2858,7 +2877,7 @@
         <v>76.0</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>140</v>
+        <v>117</v>
       </c>
     </row>
     <row r="79">
@@ -2866,7 +2885,7 @@
         <v>77.0</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>142</v>
+        <v>118</v>
       </c>
     </row>
     <row r="80">
@@ -2874,7 +2893,7 @@
         <v>78.0</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>144</v>
+        <v>119</v>
       </c>
     </row>
     <row r="81">
@@ -2882,7 +2901,7 @@
         <v>79.0</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>146</v>
+        <v>120</v>
       </c>
     </row>
     <row r="82">
@@ -2890,7 +2909,7 @@
         <v>80.0</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>148</v>
+        <v>121</v>
       </c>
     </row>
     <row r="83">
@@ -2898,7 +2917,7 @@
         <v>81.0</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>150</v>
+        <v>122</v>
       </c>
     </row>
     <row r="84">
@@ -2906,7 +2925,7 @@
         <v>82.0</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
     </row>
     <row r="85">
@@ -2914,7 +2933,7 @@
         <v>83.0</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>151</v>
+        <v>123</v>
       </c>
     </row>
     <row r="86">
@@ -2922,7 +2941,7 @@
         <v>84.0</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
     </row>
     <row r="87">
@@ -2930,7 +2949,7 @@
         <v>85.0</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>159</v>
+        <v>124</v>
       </c>
     </row>
     <row r="88">
@@ -2938,7 +2957,7 @@
         <v>86.0</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>162</v>
+        <v>125</v>
       </c>
     </row>
     <row r="89">
@@ -2946,7 +2965,7 @@
         <v>87.0</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>27</v>
+        <v>48</v>
       </c>
     </row>
     <row r="90">
@@ -2954,7 +2973,7 @@
         <v>88.0</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>165</v>
+        <v>126</v>
       </c>
     </row>
     <row r="91">
@@ -2962,7 +2981,7 @@
         <v>89.0</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>169</v>
+        <v>127</v>
       </c>
     </row>
     <row r="92">
@@ -2970,7 +2989,7 @@
         <v>90.0</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>171</v>
+        <v>128</v>
       </c>
     </row>
     <row r="93">
@@ -2978,7 +2997,7 @@
         <v>91.0</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
     </row>
     <row r="94">
@@ -2986,7 +3005,7 @@
         <v>92.0</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>176</v>
+        <v>129</v>
       </c>
     </row>
     <row r="95">
@@ -2994,7 +3013,7 @@
         <v>93.0</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>180</v>
+        <v>130</v>
       </c>
     </row>
     <row r="96">
@@ -3002,7 +3021,7 @@
         <v>94.0</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>182</v>
+        <v>131</v>
       </c>
     </row>
     <row r="97">
@@ -3010,7 +3029,7 @@
         <v>95.0</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>183</v>
+        <v>132</v>
       </c>
     </row>
     <row r="98">
@@ -3018,7 +3037,7 @@
         <v>96.0</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>185</v>
+        <v>133</v>
       </c>
     </row>
     <row r="99">
@@ -3026,7 +3045,7 @@
         <v>97.0</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>187</v>
+        <v>134</v>
       </c>
     </row>
     <row r="100">
@@ -3034,7 +3053,7 @@
         <v>98.0</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>189</v>
+        <v>135</v>
       </c>
     </row>
     <row r="101">
@@ -3042,7 +3061,7 @@
         <v>99.0</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>192</v>
+        <v>136</v>
       </c>
     </row>
     <row r="102">
@@ -3050,7 +3069,7 @@
         <v>100.0</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>54</v>
+        <v>70</v>
       </c>
     </row>
     <row r="103">
@@ -3058,7 +3077,7 @@
         <v>101.0</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>193</v>
+        <v>137</v>
       </c>
     </row>
     <row r="104">
@@ -3066,7 +3085,7 @@
         <v>102.0</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>194</v>
+        <v>138</v>
       </c>
     </row>
     <row r="105">
@@ -3074,7 +3093,7 @@
         <v>103.0</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
     </row>
     <row r="106">
@@ -3082,7 +3101,7 @@
         <v>104.0</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>72</v>
+        <v>91</v>
       </c>
     </row>
     <row r="107">
@@ -3090,7 +3109,7 @@
         <v>105.0</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
     </row>
     <row r="108">
@@ -3098,7 +3117,7 @@
         <v>106.0</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>199</v>
+        <v>139</v>
       </c>
     </row>
     <row r="109">
@@ -3106,7 +3125,7 @@
         <v>107.0</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>201</v>
+        <v>140</v>
       </c>
     </row>
     <row r="110">
@@ -3114,7 +3133,7 @@
         <v>108.0</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="111">
@@ -3122,7 +3141,7 @@
         <v>109.0</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>204</v>
+        <v>141</v>
       </c>
     </row>
     <row r="112">
@@ -3130,7 +3149,7 @@
         <v>110.0</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>206</v>
+        <v>143</v>
       </c>
     </row>
     <row r="113">
@@ -3138,7 +3157,7 @@
         <v>111.0</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>207</v>
+        <v>144</v>
       </c>
     </row>
     <row r="114">
@@ -3146,7 +3165,7 @@
         <v>112.0</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>209</v>
+        <v>145</v>
       </c>
     </row>
     <row r="115">
@@ -3154,7 +3173,7 @@
         <v>113.0</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>211</v>
+        <v>146</v>
       </c>
     </row>
     <row r="116">
@@ -3162,7 +3181,7 @@
         <v>114.0</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>212</v>
+        <v>147</v>
       </c>
     </row>
     <row r="117">
@@ -3170,7 +3189,7 @@
         <v>115.0</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>213</v>
+        <v>148</v>
       </c>
     </row>
     <row r="118">
@@ -3178,7 +3197,7 @@
         <v>116.0</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>215</v>
+        <v>149</v>
       </c>
     </row>
     <row r="119">
@@ -3186,7 +3205,7 @@
         <v>117.0</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>217</v>
+        <v>150</v>
       </c>
     </row>
     <row r="120">
@@ -3194,7 +3213,7 @@
         <v>118.0</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>220</v>
+        <v>151</v>
       </c>
     </row>
     <row r="121">
@@ -3202,7 +3221,7 @@
         <v>119.0</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>222</v>
+        <v>152</v>
       </c>
     </row>
     <row r="122">
@@ -3210,7 +3229,7 @@
         <v>120.0</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>223</v>
+        <v>153</v>
       </c>
     </row>
     <row r="123">
@@ -3218,7 +3237,7 @@
         <v>121.0</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>225</v>
+        <v>154</v>
       </c>
     </row>
     <row r="124">
@@ -3226,7 +3245,7 @@
         <v>122.0</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
     </row>
     <row r="125">
@@ -3234,7 +3253,7 @@
         <v>123.0</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>227</v>
+        <v>155</v>
       </c>
     </row>
     <row r="126">
@@ -3242,7 +3261,7 @@
         <v>124.0</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>228</v>
+        <v>156</v>
       </c>
     </row>
     <row r="127">
@@ -3250,7 +3269,7 @@
         <v>125.0</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>229</v>
+        <v>157</v>
       </c>
     </row>
     <row r="128">
@@ -3258,7 +3277,7 @@
         <v>126.0</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>230</v>
+        <v>159</v>
       </c>
     </row>
     <row r="129">
@@ -3266,7 +3285,7 @@
         <v>127.0</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>231</v>
+        <v>160</v>
       </c>
     </row>
     <row r="130">
@@ -3274,7 +3293,7 @@
         <v>128.0</v>
       </c>
       <c r="B130" s="3" t="s">
-        <v>232</v>
+        <v>161</v>
       </c>
     </row>
     <row r="131">
@@ -3282,7 +3301,7 @@
         <v>129.0</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>233</v>
+        <v>163</v>
       </c>
     </row>
     <row r="132">
@@ -3290,7 +3309,7 @@
         <v>130.0</v>
       </c>
       <c r="B132" s="3" t="s">
-        <v>235</v>
+        <v>164</v>
       </c>
     </row>
     <row r="133">
@@ -3298,7 +3317,7 @@
         <v>131.0</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>236</v>
+        <v>165</v>
       </c>
     </row>
     <row r="134">
@@ -3306,7 +3325,7 @@
         <v>132.0</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>237</v>
+        <v>166</v>
       </c>
     </row>
     <row r="135">
@@ -3314,7 +3333,7 @@
         <v>133.0</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>239</v>
+        <v>168</v>
       </c>
     </row>
     <row r="136">
@@ -3322,7 +3341,7 @@
         <v>134.0</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>242</v>
+        <v>169</v>
       </c>
     </row>
     <row r="137">
@@ -3330,7 +3349,7 @@
         <v>135.0</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>34</v>
+        <v>52</v>
       </c>
     </row>
     <row r="138">
@@ -3338,7 +3357,7 @@
         <v>136.0</v>
       </c>
       <c r="B138" s="3" t="s">
-        <v>243</v>
+        <v>171</v>
       </c>
     </row>
     <row r="139">
@@ -3346,7 +3365,7 @@
         <v>137.0</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>244</v>
+        <v>173</v>
       </c>
     </row>
     <row r="140">
@@ -3354,7 +3373,7 @@
         <v>138.0</v>
       </c>
       <c r="B140" s="3" t="s">
-        <v>246</v>
+        <v>174</v>
       </c>
     </row>
     <row r="141">
@@ -3362,7 +3381,7 @@
         <v>139.0</v>
       </c>
       <c r="B141" s="3" t="s">
-        <v>247</v>
+        <v>175</v>
       </c>
     </row>
     <row r="142">
@@ -3370,7 +3389,7 @@
         <v>140.0</v>
       </c>
       <c r="B142" s="3" t="s">
-        <v>248</v>
+        <v>176</v>
       </c>
     </row>
     <row r="143">
@@ -3378,7 +3397,7 @@
         <v>141.0</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>12</v>
+        <v>37</v>
       </c>
     </row>
     <row r="144">
@@ -3386,7 +3405,7 @@
         <v>142.0</v>
       </c>
       <c r="B144" s="3" t="s">
-        <v>250</v>
+        <v>178</v>
       </c>
     </row>
     <row r="145">
@@ -3394,7 +3413,7 @@
         <v>143.0</v>
       </c>
       <c r="B145" s="3" t="s">
-        <v>74</v>
+        <v>93</v>
       </c>
     </row>
     <row r="146">
@@ -3402,7 +3421,7 @@
         <v>144.0</v>
       </c>
       <c r="B146" s="3" t="s">
-        <v>252</v>
+        <v>181</v>
       </c>
     </row>
     <row r="147">
@@ -3410,7 +3429,7 @@
         <v>145.0</v>
       </c>
       <c r="B147" s="3" t="s">
-        <v>254</v>
+        <v>183</v>
       </c>
     </row>
     <row r="148">
@@ -3418,7 +3437,7 @@
         <v>146.0</v>
       </c>
       <c r="B148" s="3" t="s">
-        <v>255</v>
+        <v>185</v>
       </c>
     </row>
     <row r="149">
@@ -3426,7 +3445,7 @@
         <v>147.0</v>
       </c>
       <c r="B149" s="3" t="s">
-        <v>257</v>
+        <v>187</v>
       </c>
     </row>
     <row r="150">
@@ -3434,7 +3453,7 @@
         <v>148.0</v>
       </c>
       <c r="B150" s="3" t="s">
-        <v>79</v>
+        <v>97</v>
       </c>
     </row>
     <row r="151">
@@ -3442,7 +3461,7 @@
         <v>149.0</v>
       </c>
       <c r="B151" s="3" t="s">
-        <v>259</v>
+        <v>188</v>
       </c>
     </row>
     <row r="152">
@@ -3450,7 +3469,7 @@
         <v>150.0</v>
       </c>
       <c r="B152" s="3" t="s">
-        <v>83</v>
+        <v>101</v>
       </c>
     </row>
     <row r="153">
@@ -3458,7 +3477,7 @@
         <v>151.0</v>
       </c>
       <c r="B153" s="3" t="s">
-        <v>261</v>
+        <v>189</v>
       </c>
     </row>
     <row r="154">
@@ -3466,7 +3485,7 @@
         <v>152.0</v>
       </c>
       <c r="B154" s="3" t="s">
-        <v>263</v>
+        <v>190</v>
       </c>
     </row>
     <row r="155">
@@ -3474,7 +3493,7 @@
         <v>153.0</v>
       </c>
       <c r="B155" s="3" t="s">
-        <v>264</v>
+        <v>192</v>
       </c>
     </row>
     <row r="156">
@@ -3482,7 +3501,7 @@
         <v>154.0</v>
       </c>
       <c r="B156" s="3" t="s">
-        <v>265</v>
+        <v>194</v>
       </c>
     </row>
     <row r="157">
@@ -3490,7 +3509,7 @@
         <v>155.0</v>
       </c>
       <c r="B157" s="3" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
     </row>
     <row r="158">
@@ -3498,7 +3517,7 @@
         <v>156.0</v>
       </c>
       <c r="B158" s="3" t="s">
-        <v>268</v>
+        <v>196</v>
       </c>
     </row>
     <row r="159">
@@ -3506,7 +3525,7 @@
         <v>157.0</v>
       </c>
       <c r="B159" s="3" t="s">
-        <v>269</v>
+        <v>197</v>
       </c>
     </row>
     <row r="160">
@@ -3514,7 +3533,7 @@
         <v>158.0</v>
       </c>
       <c r="B160" s="3" t="s">
-        <v>271</v>
+        <v>198</v>
       </c>
     </row>
     <row r="161">
@@ -3522,7 +3541,7 @@
         <v>159.0</v>
       </c>
       <c r="B161" s="3" t="s">
-        <v>273</v>
+        <v>200</v>
       </c>
     </row>
     <row r="162">
@@ -3530,7 +3549,7 @@
         <v>160.0</v>
       </c>
       <c r="B162" s="3" t="s">
-        <v>274</v>
+        <v>201</v>
       </c>
     </row>
     <row r="163">
@@ -3538,7 +3557,7 @@
         <v>161.0</v>
       </c>
       <c r="B163" s="3" t="s">
-        <v>275</v>
+        <v>202</v>
       </c>
     </row>
     <row r="164">
@@ -3546,7 +3565,7 @@
         <v>162.0</v>
       </c>
       <c r="B164" s="3" t="s">
-        <v>277</v>
+        <v>204</v>
       </c>
     </row>
     <row r="165">
@@ -3554,7 +3573,7 @@
         <v>163.0</v>
       </c>
       <c r="B165" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="166">
@@ -3562,7 +3581,7 @@
         <v>164.0</v>
       </c>
       <c r="B166" s="3" t="s">
-        <v>280</v>
+        <v>205</v>
       </c>
     </row>
     <row r="167">
@@ -3570,7 +3589,7 @@
         <v>165.0</v>
       </c>
       <c r="B167" s="3" t="s">
-        <v>281</v>
+        <v>207</v>
       </c>
     </row>
     <row r="168">
@@ -3578,7 +3597,7 @@
         <v>166.0</v>
       </c>
       <c r="B168" s="3" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
     </row>
     <row r="169">
@@ -3586,7 +3605,7 @@
         <v>167.0</v>
       </c>
       <c r="B169" s="3" t="s">
-        <v>282</v>
+        <v>208</v>
       </c>
     </row>
     <row r="170">
@@ -3594,7 +3613,7 @@
         <v>168.0</v>
       </c>
       <c r="B170" s="3" t="s">
-        <v>284</v>
+        <v>209</v>
       </c>
     </row>
     <row r="171">
@@ -3602,7 +3621,7 @@
         <v>169.0</v>
       </c>
       <c r="B171" s="3" t="s">
-        <v>286</v>
+        <v>211</v>
       </c>
     </row>
     <row r="172">
@@ -3610,7 +3629,7 @@
         <v>170.0</v>
       </c>
       <c r="B172" s="3" t="s">
-        <v>287</v>
+        <v>213</v>
       </c>
     </row>
     <row r="173">
@@ -3618,7 +3637,7 @@
         <v>171.0</v>
       </c>
       <c r="B173" s="3" t="s">
-        <v>288</v>
+        <v>214</v>
       </c>
     </row>
     <row r="174">
@@ -3626,7 +3645,7 @@
         <v>172.0</v>
       </c>
       <c r="B174" s="3" t="s">
-        <v>290</v>
+        <v>215</v>
       </c>
     </row>
     <row r="175">
@@ -3634,7 +3653,7 @@
         <v>173.0</v>
       </c>
       <c r="B175" s="3" t="s">
-        <v>291</v>
+        <v>220</v>
       </c>
     </row>
     <row r="176">
@@ -3642,7 +3661,7 @@
         <v>174.0</v>
       </c>
       <c r="B176" s="3" t="s">
-        <v>293</v>
+        <v>221</v>
       </c>
     </row>
     <row r="177">
@@ -3650,7 +3669,7 @@
         <v>175.0</v>
       </c>
       <c r="B177" s="3" t="s">
-        <v>295</v>
+        <v>223</v>
       </c>
     </row>
     <row r="178">
@@ -3658,7 +3677,7 @@
         <v>176.0</v>
       </c>
       <c r="B178" s="3" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
     </row>
     <row r="179">
@@ -3666,7 +3685,7 @@
         <v>177.0</v>
       </c>
       <c r="B179" s="3" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
     </row>
     <row r="180">
@@ -3674,7 +3693,7 @@
         <v>178.0</v>
       </c>
       <c r="B180" s="3" t="s">
-        <v>299</v>
+        <v>226</v>
       </c>
     </row>
     <row r="181">
@@ -3682,7 +3701,7 @@
         <v>179.0</v>
       </c>
       <c r="B181" s="3" t="s">
-        <v>300</v>
+        <v>227</v>
       </c>
     </row>
     <row r="182">
@@ -3690,7 +3709,7 @@
         <v>180.0</v>
       </c>
       <c r="B182" s="3" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="183">
@@ -3698,7 +3717,7 @@
         <v>181.0</v>
       </c>
       <c r="B183" s="3" t="s">
-        <v>303</v>
+        <v>229</v>
       </c>
     </row>
     <row r="184">
@@ -3706,7 +3725,7 @@
         <v>182.0</v>
       </c>
       <c r="B184" s="3" t="s">
-        <v>46</v>
+        <v>62</v>
       </c>
     </row>
     <row r="185">
@@ -3714,7 +3733,7 @@
         <v>183.0</v>
       </c>
       <c r="B185" s="3" t="s">
-        <v>305</v>
+        <v>233</v>
       </c>
     </row>
     <row r="186">
@@ -3722,7 +3741,7 @@
         <v>184.0</v>
       </c>
       <c r="B186" s="3" t="s">
-        <v>307</v>
+        <v>234</v>
       </c>
     </row>
     <row r="187">
@@ -3730,7 +3749,7 @@
         <v>185.0</v>
       </c>
       <c r="B187" s="3" t="s">
-        <v>308</v>
+        <v>237</v>
       </c>
     </row>
     <row r="188">
@@ -3738,7 +3757,7 @@
         <v>186.0</v>
       </c>
       <c r="B188" s="3" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
     </row>
     <row r="189">
@@ -3746,7 +3765,7 @@
         <v>187.0</v>
       </c>
       <c r="B189" s="3" t="s">
-        <v>311</v>
+        <v>241</v>
       </c>
     </row>
     <row r="190">
@@ -3754,7 +3773,7 @@
         <v>188.0</v>
       </c>
       <c r="B190" s="3" t="s">
-        <v>313</v>
+        <v>244</v>
       </c>
     </row>
     <row r="191">
@@ -3762,7 +3781,7 @@
         <v>189.0</v>
       </c>
       <c r="B191" s="3" t="s">
-        <v>314</v>
+        <v>246</v>
       </c>
     </row>
     <row r="192">
@@ -3770,7 +3789,7 @@
         <v>190.0</v>
       </c>
       <c r="B192" s="3" t="s">
-        <v>315</v>
+        <v>248</v>
       </c>
     </row>
     <row r="193">
@@ -3778,7 +3797,7 @@
         <v>191.0</v>
       </c>
       <c r="B193" s="3" t="s">
-        <v>316</v>
+        <v>250</v>
       </c>
     </row>
     <row r="194">
@@ -3786,7 +3805,7 @@
         <v>192.0</v>
       </c>
       <c r="B194" s="3" t="s">
-        <v>318</v>
+        <v>251</v>
       </c>
     </row>
     <row r="195">
@@ -3794,7 +3813,7 @@
         <v>193.0</v>
       </c>
       <c r="B195" s="3" t="s">
-        <v>320</v>
+        <v>252</v>
       </c>
     </row>
     <row r="196">
@@ -3802,7 +3821,7 @@
         <v>194.0</v>
       </c>
       <c r="B196" s="3" t="s">
-        <v>321</v>
+        <v>253</v>
       </c>
     </row>
     <row r="197">
@@ -3810,7 +3829,7 @@
         <v>195.0</v>
       </c>
       <c r="B197" s="3" t="s">
-        <v>322</v>
+        <v>255</v>
       </c>
     </row>
     <row r="198">
@@ -3818,7 +3837,7 @@
         <v>196.0</v>
       </c>
       <c r="B198" s="3" t="s">
-        <v>323</v>
+        <v>256</v>
       </c>
     </row>
     <row r="199">
@@ -3826,7 +3845,7 @@
         <v>197.0</v>
       </c>
       <c r="B199" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="200">
@@ -3834,7 +3853,7 @@
         <v>198.0</v>
       </c>
       <c r="B200" s="3" t="s">
-        <v>325</v>
+        <v>257</v>
       </c>
     </row>
     <row r="201">
@@ -3842,7 +3861,7 @@
         <v>199.0</v>
       </c>
       <c r="B201" s="3" t="s">
-        <v>326</v>
+        <v>258</v>
       </c>
     </row>
   </sheetData>
@@ -3866,7 +3885,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2">
@@ -3882,7 +3901,7 @@
         <v>1.0</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>7</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4">
@@ -3890,7 +3909,7 @@
         <v>2.0</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5">
@@ -3898,7 +3917,7 @@
         <v>3.0</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6">
@@ -3906,7 +3925,7 @@
         <v>4.0</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7">
@@ -3914,7 +3933,7 @@
         <v>5.0</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8">
@@ -3922,7 +3941,7 @@
         <v>6.0</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9">
@@ -3930,7 +3949,7 @@
         <v>7.0</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10">
@@ -3938,7 +3957,7 @@
         <v>8.0</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -3958,331 +3977,331 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
     <col customWidth="1" min="2" max="2" width="38.38"/>
-    <col customWidth="1" min="3" max="3" width="29.63"/>
+    <col customWidth="1" min="3" max="3" width="42.0"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
+      <c r="A1" s="4" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2">
+      <c r="A2" s="5">
         <v>1.0</v>
       </c>
-      <c r="B2" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>100</v>
+      <c r="B2" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3">
+      <c r="A3" s="5">
         <v>2.0</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>100</v>
+      <c r="B3" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3">
+      <c r="A4" s="5">
         <v>3.0</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>100</v>
+      <c r="B4" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2">
+      <c r="A5" s="5">
         <v>4.0</v>
       </c>
-      <c r="B5" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>100</v>
+      <c r="B5" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3">
+      <c r="A6" s="5">
         <v>5.0</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>100</v>
+      <c r="B6" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3">
+      <c r="A7" s="5">
         <v>6.0</v>
       </c>
-      <c r="B7" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>100</v>
+      <c r="B7" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2">
+      <c r="A8" s="5">
         <v>7.0</v>
       </c>
-      <c r="B8" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>100</v>
+      <c r="B8" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3">
+      <c r="A9" s="5">
         <v>8.0</v>
       </c>
-      <c r="B9" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>100</v>
+      <c r="B9" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3">
+      <c r="A10" s="5">
         <v>9.0</v>
       </c>
-      <c r="B10" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>100</v>
+      <c r="B10" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2">
+      <c r="A11" s="5">
         <v>10.0</v>
       </c>
-      <c r="B11" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>100</v>
+      <c r="B11" s="8" t="s">
+        <v>254</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3">
+      <c r="A12" s="5">
         <v>11.0</v>
       </c>
-      <c r="B12" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>100</v>
+      <c r="B12" s="8" t="s">
+        <v>263</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3">
+      <c r="A13" s="5">
         <v>12.0</v>
       </c>
-      <c r="B13" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>100</v>
+      <c r="B13" s="8" t="s">
+        <v>266</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2">
+      <c r="A14" s="5">
         <v>13.0</v>
       </c>
-      <c r="B14" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>152</v>
+      <c r="B14" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>270</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3">
+      <c r="A15" s="5">
         <v>14.0</v>
       </c>
-      <c r="B15" s="7" t="s">
-        <v>155</v>
-      </c>
-      <c r="C15" s="8" t="s">
-        <v>156</v>
+      <c r="B15" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>273</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3">
+      <c r="A16" s="5">
         <v>15.0</v>
       </c>
-      <c r="B16" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="C16" s="8" t="s">
-        <v>158</v>
+      <c r="B16" s="9" t="s">
+        <v>277</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>284</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2">
+      <c r="A17" s="5">
         <v>16.0</v>
       </c>
-      <c r="B17" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="C17" s="8" t="s">
-        <v>161</v>
+      <c r="B17" s="9" t="s">
+        <v>290</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>291</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3">
+      <c r="A18" s="5">
         <v>17.0</v>
       </c>
-      <c r="B18" s="7" t="s">
-        <v>163</v>
-      </c>
-      <c r="C18" s="8" t="s">
-        <v>164</v>
+      <c r="B18" s="9" t="s">
+        <v>293</v>
+      </c>
+      <c r="C18" s="10" t="s">
+        <v>295</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3">
+      <c r="A19" s="5">
         <v>18.0</v>
       </c>
-      <c r="B19" s="7" t="s">
-        <v>166</v>
-      </c>
-      <c r="C19" s="8" t="s">
-        <v>168</v>
+      <c r="B19" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>297</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2">
+      <c r="A20" s="5">
         <v>19.0</v>
       </c>
-      <c r="B20" s="7" t="s">
-        <v>170</v>
-      </c>
-      <c r="C20" s="8" t="s">
-        <v>172</v>
+      <c r="B20" s="9" t="s">
+        <v>299</v>
+      </c>
+      <c r="C20" s="10" t="s">
+        <v>302</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3">
+      <c r="A21" s="5">
         <v>20.0</v>
       </c>
-      <c r="B21" s="7" t="s">
-        <v>174</v>
-      </c>
-      <c r="C21" s="8" t="s">
-        <v>175</v>
+      <c r="B21" s="9" t="s">
+        <v>305</v>
+      </c>
+      <c r="C21" s="10" t="s">
+        <v>306</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3">
+      <c r="A22" s="5">
         <v>21.0</v>
       </c>
-      <c r="B22" s="7" t="s">
-        <v>177</v>
-      </c>
-      <c r="C22" s="8" t="s">
-        <v>178</v>
+      <c r="B22" s="9" t="s">
+        <v>307</v>
+      </c>
+      <c r="C22" s="10" t="s">
+        <v>308</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2">
+      <c r="A23" s="5">
         <v>22.0</v>
       </c>
-      <c r="B23" s="9" t="s">
-        <v>181</v>
-      </c>
-      <c r="C23" s="10" t="s">
-        <v>186</v>
+      <c r="B23" s="11" t="s">
+        <v>309</v>
+      </c>
+      <c r="C23" s="12" t="s">
+        <v>320</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3">
+      <c r="A24" s="5">
         <v>23.0</v>
       </c>
-      <c r="B24" s="9" t="s">
-        <v>190</v>
-      </c>
-      <c r="C24" s="10" t="s">
-        <v>186</v>
+      <c r="B24" s="11" t="s">
+        <v>329</v>
+      </c>
+      <c r="C24" s="12" t="s">
+        <v>320</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3">
+      <c r="A25" s="5">
         <v>24.0</v>
       </c>
-      <c r="B25" s="9" t="s">
-        <v>195</v>
-      </c>
-      <c r="C25" s="10" t="s">
-        <v>186</v>
+      <c r="B25" s="11" t="s">
+        <v>332</v>
+      </c>
+      <c r="C25" s="12" t="s">
+        <v>320</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2">
+      <c r="A26" s="5">
         <v>25.0</v>
       </c>
-      <c r="B26" s="9" t="s">
-        <v>197</v>
-      </c>
-      <c r="C26" s="10" t="s">
-        <v>186</v>
+      <c r="B26" s="11" t="s">
+        <v>333</v>
+      </c>
+      <c r="C26" s="12" t="s">
+        <v>320</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3">
+      <c r="A27" s="5">
         <v>26.0</v>
       </c>
-      <c r="B27" s="9" t="s">
-        <v>200</v>
-      </c>
-      <c r="C27" s="10" t="s">
-        <v>186</v>
+      <c r="B27" s="11" t="s">
+        <v>335</v>
+      </c>
+      <c r="C27" s="12" t="s">
+        <v>320</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3">
+      <c r="A28" s="5">
         <v>27.0</v>
       </c>
-      <c r="B28" s="9" t="s">
-        <v>202</v>
-      </c>
-      <c r="C28" s="10" t="s">
-        <v>186</v>
+      <c r="B28" s="11" t="s">
+        <v>336</v>
+      </c>
+      <c r="C28" s="12" t="s">
+        <v>320</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2">
+      <c r="A29" s="5">
         <v>28.0</v>
       </c>
-      <c r="B29" s="9" t="s">
-        <v>205</v>
-      </c>
-      <c r="C29" s="10" t="s">
-        <v>186</v>
+      <c r="B29" s="11" t="s">
+        <v>337</v>
+      </c>
+      <c r="C29" s="12" t="s">
+        <v>320</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3">
+      <c r="A30" s="5">
         <v>29.0</v>
       </c>
-      <c r="B30" s="9" t="s">
-        <v>208</v>
-      </c>
-      <c r="C30" s="10" t="s">
-        <v>186</v>
+      <c r="B30" s="11" t="s">
+        <v>339</v>
+      </c>
+      <c r="C30" s="12" t="s">
+        <v>320</v>
       </c>
     </row>
   </sheetData>
@@ -4305,7 +4324,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>92</v>
+        <v>142</v>
       </c>
     </row>
     <row r="2">
@@ -4321,7 +4340,7 @@
         <v>1.0</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
@@ -4329,7 +4348,7 @@
         <v>2.0</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
@@ -4337,7 +4356,7 @@
         <v>3.0</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
@@ -4345,7 +4364,7 @@
         <v>4.0</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7">
@@ -4353,7 +4372,7 @@
         <v>5.0</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
@@ -4361,7 +4380,7 @@
         <v>6.0</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9">
@@ -4369,7 +4388,7 @@
         <v>7.0</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>103</v>
+        <v>158</v>
       </c>
     </row>
     <row r="10">
@@ -4377,7 +4396,7 @@
         <v>8.0</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11">
@@ -4385,7 +4404,7 @@
         <v>9.0</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>107</v>
+        <v>162</v>
       </c>
     </row>
     <row r="12">
@@ -4393,7 +4412,7 @@
         <v>10.0</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13">
@@ -4401,7 +4420,7 @@
         <v>11.0</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14">
@@ -4409,7 +4428,7 @@
         <v>12.0</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>113</v>
+        <v>167</v>
       </c>
     </row>
     <row r="15">
@@ -4417,7 +4436,7 @@
         <v>13.0</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16">
@@ -4425,7 +4444,7 @@
         <v>14.0</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>117</v>
+        <v>170</v>
       </c>
     </row>
     <row r="17">
@@ -4433,7 +4452,7 @@
         <v>15.0</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>120</v>
+        <v>172</v>
       </c>
     </row>
     <row r="18">
@@ -4441,7 +4460,7 @@
         <v>16.0</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19">
@@ -4449,7 +4468,7 @@
         <v>17.0</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20">
@@ -4457,7 +4476,7 @@
         <v>18.0</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>45</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -4465,7 +4484,7 @@
         <v>19.0</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>125</v>
+        <v>177</v>
       </c>
     </row>
     <row r="22">
@@ -4473,7 +4492,7 @@
         <v>20.0</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>126</v>
+        <v>179</v>
       </c>
     </row>
     <row r="23">
@@ -4481,7 +4500,7 @@
         <v>21.0</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
     </row>
     <row r="24">
@@ -4489,7 +4508,7 @@
         <v>22.0</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>130</v>
+        <v>184</v>
       </c>
     </row>
     <row r="25">
@@ -4497,7 +4516,7 @@
         <v>23.0</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>132</v>
+        <v>186</v>
       </c>
     </row>
     <row r="26">
@@ -4505,7 +4524,7 @@
         <v>24.0</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>49</v>
+        <v>28</v>
       </c>
     </row>
     <row r="27">
@@ -4513,7 +4532,7 @@
         <v>25.0</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>51</v>
+        <v>29</v>
       </c>
     </row>
     <row r="28">
@@ -4521,7 +4540,7 @@
         <v>26.0</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>53</v>
+        <v>32</v>
       </c>
     </row>
     <row r="29">
@@ -4529,7 +4548,7 @@
         <v>27.0</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>55</v>
+        <v>36</v>
       </c>
     </row>
     <row r="30">
@@ -4537,7 +4556,7 @@
         <v>28.0</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>16</v>
+        <v>39</v>
       </c>
     </row>
     <row r="31">
@@ -4545,7 +4564,7 @@
         <v>29.0</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>147</v>
+        <v>193</v>
       </c>
     </row>
     <row r="32">
@@ -4553,7 +4572,7 @@
         <v>30.0</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>58</v>
+        <v>41</v>
       </c>
     </row>
     <row r="33">
@@ -4561,7 +4580,7 @@
         <v>31.0</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>60</v>
+        <v>43</v>
       </c>
     </row>
     <row r="34">
@@ -4569,7 +4588,7 @@
         <v>32.0</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
     </row>
     <row r="35">
@@ -4577,7 +4596,7 @@
         <v>33.0</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
     </row>
     <row r="36">
@@ -4585,7 +4604,7 @@
         <v>34.0</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>154</v>
+        <v>199</v>
       </c>
     </row>
     <row r="37">
@@ -4593,7 +4612,7 @@
         <v>35.0</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
     </row>
     <row r="38">
@@ -4601,7 +4620,7 @@
         <v>36.0</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
     </row>
     <row r="39">
@@ -4609,7 +4628,7 @@
         <v>37.0</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>67</v>
+        <v>53</v>
       </c>
     </row>
     <row r="40">
@@ -4617,7 +4636,7 @@
         <v>38.0</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
     </row>
     <row r="41">
@@ -4625,7 +4644,7 @@
         <v>39.0</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>167</v>
+        <v>206</v>
       </c>
     </row>
     <row r="42">
@@ -4633,7 +4652,7 @@
         <v>40.0</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>70</v>
+        <v>56</v>
       </c>
     </row>
     <row r="43">
@@ -4641,7 +4660,7 @@
         <v>41.0</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>73</v>
+        <v>57</v>
       </c>
     </row>
     <row r="44">
@@ -4649,7 +4668,7 @@
         <v>42.0</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
     </row>
     <row r="45">
@@ -4657,7 +4676,7 @@
         <v>43.0</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>179</v>
+        <v>212</v>
       </c>
     </row>
     <row r="46">
@@ -4665,7 +4684,7 @@
         <v>44.0</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
     </row>
     <row r="47">
@@ -4673,7 +4692,7 @@
         <v>45.0</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>78</v>
+        <v>63</v>
       </c>
     </row>
     <row r="48">
@@ -4681,7 +4700,7 @@
         <v>46.0</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>184</v>
+        <v>217</v>
       </c>
     </row>
     <row r="49">
@@ -4689,7 +4708,7 @@
         <v>47.0</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
     </row>
     <row r="50">
@@ -4697,7 +4716,7 @@
         <v>48.0</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>188</v>
+        <v>218</v>
       </c>
     </row>
     <row r="51">
@@ -4705,7 +4724,7 @@
         <v>49.0</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
     </row>
     <row r="52">
@@ -4713,7 +4732,7 @@
         <v>50.0</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
     </row>
     <row r="53">
@@ -4721,7 +4740,7 @@
         <v>51.0</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
     </row>
     <row r="54">
@@ -4729,7 +4748,7 @@
         <v>52.0</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
     </row>
     <row r="55">
@@ -4737,7 +4756,7 @@
         <v>53.0</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>196</v>
+        <v>222</v>
       </c>
     </row>
     <row r="56">
@@ -4745,7 +4764,7 @@
         <v>54.0</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>48</v>
+        <v>64</v>
       </c>
     </row>
     <row r="57">
@@ -4753,7 +4772,7 @@
         <v>55.0</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>198</v>
+        <v>224</v>
       </c>
     </row>
     <row r="58">
@@ -4761,7 +4780,7 @@
         <v>56.0</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
     </row>
     <row r="59">
@@ -4769,7 +4788,7 @@
         <v>57.0</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
     </row>
     <row r="60">
@@ -4777,7 +4796,7 @@
         <v>58.0</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
     </row>
     <row r="61">
@@ -4785,7 +4804,7 @@
         <v>59.0</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
     </row>
     <row r="62">
@@ -4793,7 +4812,7 @@
         <v>60.0</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
     </row>
     <row r="63">
@@ -4801,7 +4820,7 @@
         <v>61.0</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
     </row>
     <row r="64">
@@ -4809,7 +4828,7 @@
         <v>62.0</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="65">
@@ -4817,7 +4836,7 @@
         <v>63.0</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
     </row>
     <row r="66">
@@ -4825,7 +4844,7 @@
         <v>64.0</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
     </row>
     <row r="67">
@@ -4833,7 +4852,7 @@
         <v>65.0</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
     </row>
     <row r="68">
@@ -4841,7 +4860,7 @@
         <v>66.0</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
     </row>
     <row r="69">
@@ -4849,7 +4868,7 @@
         <v>67.0</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>218</v>
+        <v>259</v>
       </c>
     </row>
     <row r="70">
@@ -4857,7 +4876,7 @@
         <v>68.0</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
     </row>
     <row r="71">
@@ -4865,7 +4884,7 @@
         <v>69.0</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
     </row>
     <row r="72">
@@ -4873,7 +4892,7 @@
         <v>70.0</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>62</v>
+        <v>78</v>
       </c>
     </row>
     <row r="73">
@@ -4881,7 +4900,7 @@
         <v>71.0</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>226</v>
+        <v>262</v>
       </c>
     </row>
     <row r="74">
@@ -4889,7 +4908,7 @@
         <v>72.0</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
     </row>
     <row r="75">
@@ -4897,7 +4916,7 @@
         <v>73.0</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
     </row>
     <row r="76">
@@ -4905,7 +4924,7 @@
         <v>74.0</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
     </row>
     <row r="77">
@@ -4913,7 +4932,7 @@
         <v>75.0</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
     </row>
     <row r="78">
@@ -4921,7 +4940,7 @@
         <v>76.0</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
     </row>
     <row r="79">
@@ -4929,7 +4948,7 @@
         <v>77.0</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
     </row>
     <row r="80">
@@ -4937,7 +4956,7 @@
         <v>78.0</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>234</v>
+        <v>265</v>
       </c>
     </row>
     <row r="81">
@@ -4945,7 +4964,7 @@
         <v>79.0</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
     </row>
     <row r="82">
@@ -4953,7 +4972,7 @@
         <v>80.0</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>241</v>
+        <v>269</v>
       </c>
     </row>
     <row r="83">
@@ -4961,7 +4980,7 @@
         <v>81.0</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
     </row>
     <row r="84">
@@ -4969,7 +4988,7 @@
         <v>82.0</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
     </row>
     <row r="85">
@@ -4977,7 +4996,7 @@
         <v>83.0</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>245</v>
+        <v>275</v>
       </c>
     </row>
     <row r="86">
@@ -4985,7 +5004,7 @@
         <v>84.0</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
     </row>
     <row r="87">
@@ -4993,7 +5012,7 @@
         <v>85.0</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
     </row>
     <row r="88">
@@ -5001,7 +5020,7 @@
         <v>86.0</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="89">
@@ -5009,7 +5028,7 @@
         <v>87.0</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
     </row>
     <row r="90">
@@ -5017,7 +5036,7 @@
         <v>88.0</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>124</v>
+        <v>110</v>
       </c>
     </row>
     <row r="91">
@@ -5025,7 +5044,7 @@
         <v>89.0</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="92">
@@ -5033,7 +5052,7 @@
         <v>90.0</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="93">
@@ -5041,7 +5060,7 @@
         <v>91.0</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>128</v>
+        <v>111</v>
       </c>
     </row>
     <row r="94">
@@ -5049,7 +5068,7 @@
         <v>92.0</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="95">
@@ -5057,7 +5076,7 @@
         <v>93.0</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>131</v>
+        <v>112</v>
       </c>
     </row>
     <row r="96">
@@ -5065,7 +5084,7 @@
         <v>94.0</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>134</v>
+        <v>113</v>
       </c>
     </row>
     <row r="97">
@@ -5073,7 +5092,7 @@
         <v>95.0</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>135</v>
+        <v>114</v>
       </c>
     </row>
     <row r="98">
@@ -5081,7 +5100,7 @@
         <v>96.0</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>136</v>
+        <v>115</v>
       </c>
     </row>
     <row r="99">
@@ -5089,7 +5108,7 @@
         <v>97.0</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>139</v>
+        <v>116</v>
       </c>
     </row>
     <row r="100">
@@ -5097,7 +5116,7 @@
         <v>98.0</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>140</v>
+        <v>117</v>
       </c>
     </row>
     <row r="101">
@@ -5105,7 +5124,7 @@
         <v>99.0</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>142</v>
+        <v>118</v>
       </c>
     </row>
     <row r="102">
@@ -5113,7 +5132,7 @@
         <v>100.0</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>266</v>
+        <v>285</v>
       </c>
     </row>
     <row r="103">
@@ -5121,7 +5140,7 @@
         <v>101.0</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>144</v>
+        <v>119</v>
       </c>
     </row>
     <row r="104">
@@ -5129,7 +5148,7 @@
         <v>102.0</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>146</v>
+        <v>120</v>
       </c>
     </row>
     <row r="105">
@@ -5137,7 +5156,7 @@
         <v>103.0</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>270</v>
+        <v>286</v>
       </c>
     </row>
     <row r="106">
@@ -5145,7 +5164,7 @@
         <v>104.0</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>148</v>
+        <v>121</v>
       </c>
     </row>
     <row r="107">
@@ -5153,7 +5172,7 @@
         <v>105.0</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>150</v>
+        <v>122</v>
       </c>
     </row>
     <row r="108">
@@ -5161,7 +5180,7 @@
         <v>106.0</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
     </row>
     <row r="109">
@@ -5169,7 +5188,7 @@
         <v>107.0</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>151</v>
+        <v>123</v>
       </c>
     </row>
     <row r="110">
@@ -5177,7 +5196,7 @@
         <v>108.0</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>278</v>
+        <v>292</v>
       </c>
     </row>
     <row r="111">
@@ -5185,7 +5204,7 @@
         <v>109.0</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
     </row>
     <row r="112">
@@ -5193,7 +5212,7 @@
         <v>110.0</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>159</v>
+        <v>124</v>
       </c>
     </row>
     <row r="113">
@@ -5201,7 +5220,7 @@
         <v>111.0</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>162</v>
+        <v>125</v>
       </c>
     </row>
     <row r="114">
@@ -5209,7 +5228,7 @@
         <v>112.0</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>283</v>
+        <v>300</v>
       </c>
     </row>
     <row r="115">
@@ -5217,7 +5236,7 @@
         <v>113.0</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>285</v>
+        <v>303</v>
       </c>
     </row>
     <row r="116">
@@ -5225,7 +5244,7 @@
         <v>114.0</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>27</v>
+        <v>48</v>
       </c>
     </row>
     <row r="117">
@@ -5233,7 +5252,7 @@
         <v>115.0</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>165</v>
+        <v>126</v>
       </c>
     </row>
     <row r="118">
@@ -5241,7 +5260,7 @@
         <v>116.0</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>169</v>
+        <v>127</v>
       </c>
     </row>
     <row r="119">
@@ -5249,7 +5268,7 @@
         <v>117.0</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>171</v>
+        <v>128</v>
       </c>
     </row>
     <row r="120">
@@ -5257,7 +5276,7 @@
         <v>118.0</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>296</v>
+        <v>311</v>
       </c>
     </row>
     <row r="121">
@@ -5265,7 +5284,7 @@
         <v>119.0</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>297</v>
+        <v>313</v>
       </c>
     </row>
     <row r="122">
@@ -5273,7 +5292,7 @@
         <v>120.0</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
     </row>
     <row r="123">
@@ -5281,7 +5300,7 @@
         <v>121.0</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>176</v>
+        <v>129</v>
       </c>
     </row>
     <row r="124">
@@ -5289,7 +5308,7 @@
         <v>122.0</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>180</v>
+        <v>130</v>
       </c>
     </row>
     <row r="125">
@@ -5297,7 +5316,7 @@
         <v>123.0</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>182</v>
+        <v>131</v>
       </c>
     </row>
     <row r="126">
@@ -5305,7 +5324,7 @@
         <v>124.0</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>306</v>
+        <v>315</v>
       </c>
     </row>
     <row r="127">
@@ -5313,7 +5332,7 @@
         <v>125.0</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>309</v>
+        <v>316</v>
       </c>
     </row>
     <row r="128">
@@ -5321,7 +5340,7 @@
         <v>126.0</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>183</v>
+        <v>132</v>
       </c>
     </row>
     <row r="129">
@@ -5329,7 +5348,7 @@
         <v>127.0</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>185</v>
+        <v>133</v>
       </c>
     </row>
     <row r="130">
@@ -5337,7 +5356,7 @@
         <v>128.0</v>
       </c>
       <c r="B130" s="3" t="s">
-        <v>187</v>
+        <v>134</v>
       </c>
     </row>
     <row r="131">
@@ -5345,7 +5364,7 @@
         <v>129.0</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>189</v>
+        <v>135</v>
       </c>
     </row>
     <row r="132">
@@ -5353,7 +5372,7 @@
         <v>130.0</v>
       </c>
       <c r="B132" s="3" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="133">
@@ -5361,7 +5380,7 @@
         <v>131.0</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>192</v>
+        <v>136</v>
       </c>
     </row>
     <row r="134">
@@ -5369,7 +5388,7 @@
         <v>132.0</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>54</v>
+        <v>70</v>
       </c>
     </row>
     <row r="135">
@@ -5377,7 +5396,7 @@
         <v>133.0</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>327</v>
+        <v>319</v>
       </c>
     </row>
     <row r="136">
@@ -5385,7 +5404,7 @@
         <v>134.0</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>193</v>
+        <v>137</v>
       </c>
     </row>
     <row r="137">
@@ -5393,7 +5412,7 @@
         <v>135.0</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>194</v>
+        <v>138</v>
       </c>
     </row>
     <row r="138">
@@ -5401,7 +5420,7 @@
         <v>136.0</v>
       </c>
       <c r="B138" s="3" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
     </row>
     <row r="139">
@@ -5409,7 +5428,7 @@
         <v>137.0</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
     </row>
     <row r="140">
@@ -5417,7 +5436,7 @@
         <v>138.0</v>
       </c>
       <c r="B140" s="3" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
     </row>
     <row r="141">
@@ -5425,7 +5444,7 @@
         <v>139.0</v>
       </c>
       <c r="B141" s="3" t="s">
-        <v>72</v>
+        <v>91</v>
       </c>
     </row>
     <row r="142">
@@ -5433,7 +5452,7 @@
         <v>140.0</v>
       </c>
       <c r="B142" s="3" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
     </row>
     <row r="143">
@@ -5441,7 +5460,7 @@
         <v>141.0</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
     </row>
     <row r="144">
@@ -5449,7 +5468,7 @@
         <v>142.0</v>
       </c>
       <c r="B144" s="3" t="s">
-        <v>335</v>
+        <v>328</v>
       </c>
     </row>
     <row r="145">
@@ -5457,7 +5476,7 @@
         <v>143.0</v>
       </c>
       <c r="B145" s="3" t="s">
-        <v>199</v>
+        <v>139</v>
       </c>
     </row>
     <row r="146">
@@ -5465,7 +5484,7 @@
         <v>144.0</v>
       </c>
       <c r="B146" s="3" t="s">
-        <v>201</v>
+        <v>140</v>
       </c>
     </row>
     <row r="147">
@@ -5473,7 +5492,7 @@
         <v>145.0</v>
       </c>
       <c r="B147" s="3" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="148">
@@ -5481,7 +5500,7 @@
         <v>146.0</v>
       </c>
       <c r="B148" s="3" t="s">
-        <v>204</v>
+        <v>141</v>
       </c>
     </row>
     <row r="149">
@@ -5489,7 +5508,7 @@
         <v>147.0</v>
       </c>
       <c r="B149" s="3" t="s">
-        <v>206</v>
+        <v>143</v>
       </c>
     </row>
     <row r="150">
@@ -5497,7 +5516,7 @@
         <v>148.0</v>
       </c>
       <c r="B150" s="3" t="s">
-        <v>207</v>
+        <v>144</v>
       </c>
     </row>
     <row r="151">
@@ -5505,7 +5524,7 @@
         <v>149.0</v>
       </c>
       <c r="B151" s="3" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
     </row>
     <row r="152">
@@ -5513,7 +5532,7 @@
         <v>150.0</v>
       </c>
       <c r="B152" s="3" t="s">
-        <v>209</v>
+        <v>145</v>
       </c>
     </row>
     <row r="153">
@@ -5521,7 +5540,7 @@
         <v>151.0</v>
       </c>
       <c r="B153" s="3" t="s">
-        <v>211</v>
+        <v>146</v>
       </c>
     </row>
     <row r="154">
@@ -5529,7 +5548,7 @@
         <v>152.0</v>
       </c>
       <c r="B154" s="3" t="s">
-        <v>212</v>
+        <v>147</v>
       </c>
     </row>
     <row r="155">
@@ -5537,7 +5556,7 @@
         <v>153.0</v>
       </c>
       <c r="B155" s="3" t="s">
-        <v>213</v>
+        <v>148</v>
       </c>
     </row>
     <row r="156">
@@ -5545,7 +5564,7 @@
         <v>154.0</v>
       </c>
       <c r="B156" s="3" t="s">
-        <v>215</v>
+        <v>149</v>
       </c>
     </row>
     <row r="157">
@@ -5553,7 +5572,7 @@
         <v>155.0</v>
       </c>
       <c r="B157" s="3" t="s">
-        <v>217</v>
+        <v>150</v>
       </c>
     </row>
     <row r="158">
@@ -5561,7 +5580,7 @@
         <v>156.0</v>
       </c>
       <c r="B158" s="3" t="s">
-        <v>220</v>
+        <v>151</v>
       </c>
     </row>
     <row r="159">
@@ -5569,7 +5588,7 @@
         <v>157.0</v>
       </c>
       <c r="B159" s="3" t="s">
-        <v>222</v>
+        <v>152</v>
       </c>
     </row>
     <row r="160">
@@ -5577,7 +5596,7 @@
         <v>158.0</v>
       </c>
       <c r="B160" s="3" t="s">
-        <v>223</v>
+        <v>153</v>
       </c>
     </row>
     <row r="161">
@@ -5585,7 +5604,7 @@
         <v>159.0</v>
       </c>
       <c r="B161" s="3" t="s">
-        <v>225</v>
+        <v>154</v>
       </c>
     </row>
     <row r="162">
@@ -5593,7 +5612,7 @@
         <v>160.0</v>
       </c>
       <c r="B162" s="3" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
     </row>
     <row r="163">
@@ -5601,7 +5620,7 @@
         <v>161.0</v>
       </c>
       <c r="B163" s="3" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
     </row>
     <row r="164">
@@ -5609,7 +5628,7 @@
         <v>162.0</v>
       </c>
       <c r="B164" s="3" t="s">
-        <v>227</v>
+        <v>155</v>
       </c>
     </row>
     <row r="165">
@@ -5617,7 +5636,7 @@
         <v>163.0</v>
       </c>
       <c r="B165" s="3" t="s">
-        <v>228</v>
+        <v>156</v>
       </c>
     </row>
     <row r="166">
@@ -5625,7 +5644,7 @@
         <v>164.0</v>
       </c>
       <c r="B166" s="3" t="s">
-        <v>229</v>
+        <v>157</v>
       </c>
     </row>
     <row r="167">
@@ -5633,7 +5652,7 @@
         <v>165.0</v>
       </c>
       <c r="B167" s="3" t="s">
-        <v>230</v>
+        <v>159</v>
       </c>
     </row>
     <row r="168">
@@ -5641,7 +5660,7 @@
         <v>166.0</v>
       </c>
       <c r="B168" s="3" t="s">
-        <v>231</v>
+        <v>160</v>
       </c>
     </row>
     <row r="169">
@@ -5649,7 +5668,7 @@
         <v>167.0</v>
       </c>
       <c r="B169" s="3" t="s">
-        <v>232</v>
+        <v>161</v>
       </c>
     </row>
     <row r="170">
@@ -5657,7 +5676,7 @@
         <v>168.0</v>
       </c>
       <c r="B170" s="3" t="s">
-        <v>235</v>
+        <v>164</v>
       </c>
     </row>
     <row r="171">
@@ -5665,7 +5684,7 @@
         <v>169.0</v>
       </c>
       <c r="B171" s="3" t="s">
-        <v>236</v>
+        <v>165</v>
       </c>
     </row>
     <row r="172">
@@ -5673,7 +5692,7 @@
         <v>170.0</v>
       </c>
       <c r="B172" s="3" t="s">
-        <v>237</v>
+        <v>166</v>
       </c>
     </row>
     <row r="173">
@@ -5681,7 +5700,7 @@
         <v>171.0</v>
       </c>
       <c r="B173" s="3" t="s">
-        <v>239</v>
+        <v>168</v>
       </c>
     </row>
     <row r="174">
@@ -5689,7 +5708,7 @@
         <v>172.0</v>
       </c>
       <c r="B174" s="3" t="s">
-        <v>242</v>
+        <v>169</v>
       </c>
     </row>
     <row r="175">
@@ -5697,7 +5716,7 @@
         <v>173.0</v>
       </c>
       <c r="B175" s="3" t="s">
-        <v>34</v>
+        <v>52</v>
       </c>
     </row>
     <row r="176">
@@ -5713,7 +5732,7 @@
         <v>175.0</v>
       </c>
       <c r="B177" s="3" t="s">
-        <v>243</v>
+        <v>171</v>
       </c>
     </row>
     <row r="178">
@@ -5729,7 +5748,7 @@
         <v>177.0</v>
       </c>
       <c r="B179" s="3" t="s">
-        <v>244</v>
+        <v>173</v>
       </c>
     </row>
     <row r="180">
@@ -5737,7 +5756,7 @@
         <v>178.0</v>
       </c>
       <c r="B180" s="3" t="s">
-        <v>246</v>
+        <v>174</v>
       </c>
     </row>
     <row r="181">
@@ -5745,7 +5764,7 @@
         <v>179.0</v>
       </c>
       <c r="B181" s="3" t="s">
-        <v>247</v>
+        <v>175</v>
       </c>
     </row>
     <row r="182">
@@ -5753,7 +5772,7 @@
         <v>180.0</v>
       </c>
       <c r="B182" s="3" t="s">
-        <v>248</v>
+        <v>176</v>
       </c>
     </row>
     <row r="183">
@@ -5761,7 +5780,7 @@
         <v>181.0</v>
       </c>
       <c r="B183" s="3" t="s">
-        <v>12</v>
+        <v>37</v>
       </c>
     </row>
     <row r="184">
@@ -5769,7 +5788,7 @@
         <v>182.0</v>
       </c>
       <c r="B184" s="3" t="s">
-        <v>250</v>
+        <v>178</v>
       </c>
     </row>
     <row r="185">
@@ -5777,7 +5796,7 @@
         <v>183.0</v>
       </c>
       <c r="B185" s="3" t="s">
-        <v>74</v>
+        <v>93</v>
       </c>
     </row>
     <row r="186">
@@ -5785,7 +5804,7 @@
         <v>184.0</v>
       </c>
       <c r="B186" s="3" t="s">
-        <v>252</v>
+        <v>181</v>
       </c>
     </row>
     <row r="187">
@@ -5793,7 +5812,7 @@
         <v>185.0</v>
       </c>
       <c r="B187" s="3" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="188">
@@ -5801,7 +5820,7 @@
         <v>186.0</v>
       </c>
       <c r="B188" s="3" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="189">
@@ -5809,7 +5828,7 @@
         <v>187.0</v>
       </c>
       <c r="B189" s="3" t="s">
-        <v>254</v>
+        <v>183</v>
       </c>
     </row>
     <row r="190">
@@ -5817,7 +5836,7 @@
         <v>188.0</v>
       </c>
       <c r="B190" s="3" t="s">
-        <v>255</v>
+        <v>185</v>
       </c>
     </row>
     <row r="191">
@@ -5825,7 +5844,7 @@
         <v>189.0</v>
       </c>
       <c r="B191" s="3" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="192">
@@ -5833,7 +5852,7 @@
         <v>190.0</v>
       </c>
       <c r="B192" s="3" t="s">
-        <v>257</v>
+        <v>187</v>
       </c>
     </row>
     <row r="193">
@@ -5841,7 +5860,7 @@
         <v>191.0</v>
       </c>
       <c r="B193" s="3" t="s">
-        <v>79</v>
+        <v>97</v>
       </c>
     </row>
     <row r="194">
@@ -5849,7 +5868,7 @@
         <v>192.0</v>
       </c>
       <c r="B194" s="3" t="s">
-        <v>259</v>
+        <v>188</v>
       </c>
     </row>
     <row r="195">
@@ -5857,7 +5876,7 @@
         <v>193.0</v>
       </c>
       <c r="B195" s="3" t="s">
-        <v>83</v>
+        <v>101</v>
       </c>
     </row>
     <row r="196">
@@ -5873,7 +5892,7 @@
         <v>195.0</v>
       </c>
       <c r="B197" s="3" t="s">
-        <v>261</v>
+        <v>189</v>
       </c>
     </row>
     <row r="198">
@@ -5881,7 +5900,7 @@
         <v>196.0</v>
       </c>
       <c r="B198" s="3" t="s">
-        <v>263</v>
+        <v>190</v>
       </c>
     </row>
     <row r="199">
@@ -5889,7 +5908,7 @@
         <v>197.0</v>
       </c>
       <c r="B199" s="3" t="s">
-        <v>264</v>
+        <v>192</v>
       </c>
     </row>
     <row r="200">
@@ -5897,7 +5916,7 @@
         <v>198.0</v>
       </c>
       <c r="B200" s="3" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
     </row>
     <row r="201">
@@ -5905,7 +5924,7 @@
         <v>199.0</v>
       </c>
       <c r="B201" s="3" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="202">
@@ -5913,7 +5932,7 @@
         <v>200.0</v>
       </c>
       <c r="B202" s="3" t="s">
-        <v>265</v>
+        <v>194</v>
       </c>
     </row>
     <row r="203">
@@ -5921,7 +5940,7 @@
         <v>201.0</v>
       </c>
       <c r="B203" s="3" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
     </row>
     <row r="204">
@@ -5929,7 +5948,7 @@
         <v>202.0</v>
       </c>
       <c r="B204" s="3" t="s">
-        <v>268</v>
+        <v>196</v>
       </c>
     </row>
     <row r="205">
@@ -5937,7 +5956,7 @@
         <v>203.0</v>
       </c>
       <c r="B205" s="3" t="s">
-        <v>269</v>
+        <v>197</v>
       </c>
     </row>
     <row r="206">
@@ -5945,7 +5964,7 @@
         <v>204.0</v>
       </c>
       <c r="B206" s="3" t="s">
-        <v>271</v>
+        <v>198</v>
       </c>
     </row>
     <row r="207">
@@ -5953,7 +5972,7 @@
         <v>205.0</v>
       </c>
       <c r="B207" s="3" t="s">
-        <v>273</v>
+        <v>200</v>
       </c>
     </row>
     <row r="208">
@@ -5961,7 +5980,7 @@
         <v>206.0</v>
       </c>
       <c r="B208" s="3" t="s">
-        <v>274</v>
+        <v>201</v>
       </c>
     </row>
     <row r="209">
@@ -5969,7 +5988,7 @@
         <v>207.0</v>
       </c>
       <c r="B209" s="3" t="s">
-        <v>275</v>
+        <v>202</v>
       </c>
     </row>
     <row r="210">
@@ -5977,7 +5996,7 @@
         <v>208.0</v>
       </c>
       <c r="B210" s="3" t="s">
-        <v>277</v>
+        <v>204</v>
       </c>
     </row>
     <row r="211">
@@ -5985,7 +6004,7 @@
         <v>209.0</v>
       </c>
       <c r="B211" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="212">
@@ -6001,7 +6020,7 @@
         <v>211.0</v>
       </c>
       <c r="B213" s="3" t="s">
-        <v>280</v>
+        <v>205</v>
       </c>
     </row>
     <row r="214">
@@ -6017,7 +6036,7 @@
         <v>213.0</v>
       </c>
       <c r="B215" s="3" t="s">
-        <v>281</v>
+        <v>207</v>
       </c>
     </row>
     <row r="216">
@@ -6033,7 +6052,7 @@
         <v>215.0</v>
       </c>
       <c r="B217" s="3" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
     </row>
     <row r="218">
@@ -6041,7 +6060,7 @@
         <v>216.0</v>
       </c>
       <c r="B218" s="3" t="s">
-        <v>282</v>
+        <v>208</v>
       </c>
     </row>
     <row r="219">
@@ -6049,7 +6068,7 @@
         <v>217.0</v>
       </c>
       <c r="B219" s="3" t="s">
-        <v>284</v>
+        <v>209</v>
       </c>
     </row>
     <row r="220">
@@ -6057,7 +6076,7 @@
         <v>218.0</v>
       </c>
       <c r="B220" s="3" t="s">
-        <v>286</v>
+        <v>211</v>
       </c>
     </row>
     <row r="221">
@@ -6065,7 +6084,7 @@
         <v>219.0</v>
       </c>
       <c r="B221" s="3" t="s">
-        <v>287</v>
+        <v>213</v>
       </c>
     </row>
     <row r="222">
@@ -6081,7 +6100,7 @@
         <v>221.0</v>
       </c>
       <c r="B223" s="3" t="s">
-        <v>288</v>
+        <v>214</v>
       </c>
     </row>
     <row r="224">
@@ -6089,7 +6108,7 @@
         <v>222.0</v>
       </c>
       <c r="B224" s="3" t="s">
-        <v>290</v>
+        <v>215</v>
       </c>
     </row>
     <row r="225">
@@ -6097,7 +6116,7 @@
         <v>223.0</v>
       </c>
       <c r="B225" s="3" t="s">
-        <v>291</v>
+        <v>220</v>
       </c>
     </row>
     <row r="226">
@@ -6105,7 +6124,7 @@
         <v>224.0</v>
       </c>
       <c r="B226" s="3" t="s">
-        <v>293</v>
+        <v>221</v>
       </c>
     </row>
     <row r="227">
@@ -6113,7 +6132,7 @@
         <v>225.0</v>
       </c>
       <c r="B227" s="3" t="s">
-        <v>295</v>
+        <v>223</v>
       </c>
     </row>
     <row r="228">
@@ -6121,7 +6140,7 @@
         <v>226.0</v>
       </c>
       <c r="B228" s="3" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
     </row>
     <row r="229">
@@ -6129,7 +6148,7 @@
         <v>227.0</v>
       </c>
       <c r="B229" s="3" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
     </row>
     <row r="230">
@@ -6137,7 +6156,7 @@
         <v>228.0</v>
       </c>
       <c r="B230" s="3" t="s">
-        <v>299</v>
+        <v>226</v>
       </c>
     </row>
     <row r="231">
@@ -6145,7 +6164,7 @@
         <v>229.0</v>
       </c>
       <c r="B231" s="3" t="s">
-        <v>300</v>
+        <v>227</v>
       </c>
     </row>
     <row r="232">
@@ -6153,7 +6172,7 @@
         <v>230.0</v>
       </c>
       <c r="B232" s="3" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="233">
@@ -6161,7 +6180,7 @@
         <v>231.0</v>
       </c>
       <c r="B233" s="3" t="s">
-        <v>303</v>
+        <v>229</v>
       </c>
     </row>
     <row r="234">
@@ -6169,7 +6188,7 @@
         <v>232.0</v>
       </c>
       <c r="B234" s="3" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
     </row>
     <row r="235">
@@ -6177,7 +6196,7 @@
         <v>233.0</v>
       </c>
       <c r="B235" s="3" t="s">
-        <v>46</v>
+        <v>62</v>
       </c>
     </row>
     <row r="236">
@@ -6185,7 +6204,7 @@
         <v>234.0</v>
       </c>
       <c r="B236" s="3" t="s">
-        <v>305</v>
+        <v>233</v>
       </c>
     </row>
     <row r="237">
@@ -6193,7 +6212,7 @@
         <v>235.0</v>
       </c>
       <c r="B237" s="3" t="s">
-        <v>307</v>
+        <v>234</v>
       </c>
     </row>
     <row r="238">
@@ -6201,7 +6220,7 @@
         <v>236.0</v>
       </c>
       <c r="B238" s="3" t="s">
-        <v>308</v>
+        <v>237</v>
       </c>
     </row>
     <row r="239">
@@ -6209,7 +6228,7 @@
         <v>237.0</v>
       </c>
       <c r="B239" s="3" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="240">
@@ -6217,7 +6236,7 @@
         <v>238.0</v>
       </c>
       <c r="B240" s="3" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
     </row>
     <row r="241">
@@ -6225,7 +6244,7 @@
         <v>239.0</v>
       </c>
       <c r="B241" s="3" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
     </row>
     <row r="242">
@@ -6233,7 +6252,7 @@
         <v>240.0</v>
       </c>
       <c r="B242" s="3" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="243">
@@ -6241,7 +6260,7 @@
         <v>241.0</v>
       </c>
       <c r="B243" s="3" t="s">
-        <v>311</v>
+        <v>241</v>
       </c>
     </row>
     <row r="244">
@@ -6249,7 +6268,7 @@
         <v>242.0</v>
       </c>
       <c r="B244" s="3" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="245">
@@ -6257,7 +6276,7 @@
         <v>243.0</v>
       </c>
       <c r="B245" s="3" t="s">
-        <v>313</v>
+        <v>244</v>
       </c>
     </row>
     <row r="246">
@@ -6265,7 +6284,7 @@
         <v>244.0</v>
       </c>
       <c r="B246" s="3" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="247">
@@ -6273,7 +6292,7 @@
         <v>245.0</v>
       </c>
       <c r="B247" s="3" t="s">
-        <v>314</v>
+        <v>246</v>
       </c>
     </row>
     <row r="248">
@@ -6281,7 +6300,7 @@
         <v>246.0</v>
       </c>
       <c r="B248" s="3" t="s">
-        <v>315</v>
+        <v>248</v>
       </c>
     </row>
     <row r="249">
@@ -6289,7 +6308,7 @@
         <v>247.0</v>
       </c>
       <c r="B249" s="3" t="s">
-        <v>316</v>
+        <v>250</v>
       </c>
     </row>
     <row r="250">
@@ -6297,7 +6316,7 @@
         <v>248.0</v>
       </c>
       <c r="B250" s="3" t="s">
-        <v>318</v>
+        <v>251</v>
       </c>
     </row>
     <row r="251">
@@ -6305,7 +6324,7 @@
         <v>249.0</v>
       </c>
       <c r="B251" s="3" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
     </row>
     <row r="252">
@@ -6313,7 +6332,7 @@
         <v>250.0</v>
       </c>
       <c r="B252" s="3" t="s">
-        <v>320</v>
+        <v>252</v>
       </c>
     </row>
     <row r="253">
@@ -6321,7 +6340,7 @@
         <v>251.0</v>
       </c>
       <c r="B253" s="3" t="s">
-        <v>321</v>
+        <v>253</v>
       </c>
     </row>
     <row r="254">
@@ -6329,7 +6348,7 @@
         <v>252.0</v>
       </c>
       <c r="B254" s="3" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
     <row r="255">
@@ -6337,7 +6356,7 @@
         <v>253.0</v>
       </c>
       <c r="B255" s="3" t="s">
-        <v>322</v>
+        <v>255</v>
       </c>
     </row>
     <row r="256">
@@ -6345,7 +6364,7 @@
         <v>254.0</v>
       </c>
       <c r="B256" s="3" t="s">
-        <v>323</v>
+        <v>256</v>
       </c>
     </row>
     <row r="257">
@@ -6353,7 +6372,7 @@
         <v>255.0</v>
       </c>
       <c r="B257" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="258">
@@ -6361,7 +6380,7 @@
         <v>256.0</v>
       </c>
       <c r="B258" s="3" t="s">
-        <v>325</v>
+        <v>257</v>
       </c>
     </row>
     <row r="259">
@@ -6369,7 +6388,7 @@
         <v>257.0</v>
       </c>
       <c r="B259" s="3" t="s">
-        <v>326</v>
+        <v>258</v>
       </c>
     </row>
     <row r="260">
@@ -6402,7 +6421,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>123</v>
+        <v>180</v>
       </c>
     </row>
     <row r="2">
@@ -6418,7 +6437,7 @@
         <v>1.0</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
@@ -6426,7 +6445,7 @@
         <v>2.0</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
@@ -6434,7 +6453,7 @@
         <v>3.0</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>137</v>
+        <v>191</v>
       </c>
     </row>
     <row r="6">
@@ -6442,7 +6461,7 @@
         <v>4.0</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7">
@@ -6450,7 +6469,7 @@
         <v>5.0</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>141</v>
+        <v>195</v>
       </c>
     </row>
     <row r="8">
@@ -6458,7 +6477,7 @@
         <v>6.0</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9">
@@ -6466,7 +6485,7 @@
         <v>7.0</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10">
@@ -6474,7 +6493,7 @@
         <v>8.0</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11">
@@ -6482,7 +6501,7 @@
         <v>9.0</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>103</v>
+        <v>158</v>
       </c>
     </row>
     <row r="12">
@@ -6490,7 +6509,7 @@
         <v>10.0</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13">
@@ -6498,7 +6517,7 @@
         <v>11.0</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>107</v>
+        <v>162</v>
       </c>
     </row>
     <row r="14">
@@ -6506,7 +6525,7 @@
         <v>12.0</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>153</v>
+        <v>203</v>
       </c>
     </row>
     <row r="15">
@@ -6514,7 +6533,7 @@
         <v>13.0</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16">
@@ -6522,7 +6541,7 @@
         <v>14.0</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
     </row>
     <row r="17">
@@ -6530,7 +6549,7 @@
         <v>15.0</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>113</v>
+        <v>167</v>
       </c>
     </row>
     <row r="18">
@@ -6538,7 +6557,7 @@
         <v>16.0</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19">
@@ -6546,7 +6565,7 @@
         <v>17.0</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>117</v>
+        <v>170</v>
       </c>
     </row>
     <row r="20">
@@ -6554,7 +6573,7 @@
         <v>18.0</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>120</v>
+        <v>172</v>
       </c>
     </row>
     <row r="21">
@@ -6562,7 +6581,7 @@
         <v>19.0</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>173</v>
+        <v>210</v>
       </c>
     </row>
     <row r="22">
@@ -6570,7 +6589,7 @@
         <v>20.0</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23">
@@ -6578,7 +6597,7 @@
         <v>21.0</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
     </row>
     <row r="24">
@@ -6586,7 +6605,7 @@
         <v>22.0</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>45</v>
+        <v>23</v>
       </c>
     </row>
     <row r="25">
@@ -6594,7 +6613,7 @@
         <v>23.0</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>125</v>
+        <v>177</v>
       </c>
     </row>
     <row r="26">
@@ -6602,7 +6621,7 @@
         <v>24.0</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>126</v>
+        <v>179</v>
       </c>
     </row>
     <row r="27">
@@ -6610,7 +6629,7 @@
         <v>25.0</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>191</v>
+        <v>219</v>
       </c>
     </row>
     <row r="28">
@@ -6618,7 +6637,7 @@
         <v>26.0</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
     </row>
     <row r="29">
@@ -6626,7 +6645,7 @@
         <v>27.0</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>130</v>
+        <v>184</v>
       </c>
     </row>
     <row r="30">
@@ -6634,7 +6653,7 @@
         <v>28.0</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>132</v>
+        <v>186</v>
       </c>
     </row>
     <row r="31">
@@ -6642,7 +6661,7 @@
         <v>29.0</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>49</v>
+        <v>28</v>
       </c>
     </row>
     <row r="32">
@@ -6650,7 +6669,7 @@
         <v>30.0</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>51</v>
+        <v>29</v>
       </c>
     </row>
     <row r="33">
@@ -6658,7 +6677,7 @@
         <v>31.0</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>53</v>
+        <v>32</v>
       </c>
     </row>
     <row r="34">
@@ -6666,7 +6685,7 @@
         <v>32.0</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>203</v>
+        <v>225</v>
       </c>
     </row>
     <row r="35">
@@ -6674,7 +6693,7 @@
         <v>33.0</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>55</v>
+        <v>36</v>
       </c>
     </row>
     <row r="36">
@@ -6682,7 +6701,7 @@
         <v>34.0</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>16</v>
+        <v>39</v>
       </c>
     </row>
     <row r="37">
@@ -6690,7 +6709,7 @@
         <v>35.0</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>147</v>
+        <v>193</v>
       </c>
     </row>
     <row r="38">
@@ -6698,7 +6717,7 @@
         <v>36.0</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>210</v>
+        <v>231</v>
       </c>
     </row>
     <row r="39">
@@ -6706,7 +6725,7 @@
         <v>37.0</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>58</v>
+        <v>41</v>
       </c>
     </row>
     <row r="40">
@@ -6714,7 +6733,7 @@
         <v>38.0</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>60</v>
+        <v>43</v>
       </c>
     </row>
     <row r="41">
@@ -6722,7 +6741,7 @@
         <v>39.0</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>214</v>
+        <v>235</v>
       </c>
     </row>
     <row r="42">
@@ -6730,7 +6749,7 @@
         <v>40.0</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>216</v>
+        <v>238</v>
       </c>
     </row>
     <row r="43">
@@ -6738,7 +6757,7 @@
         <v>41.0</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>219</v>
+        <v>240</v>
       </c>
     </row>
     <row r="44">
@@ -6746,7 +6765,7 @@
         <v>42.0</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>221</v>
+        <v>243</v>
       </c>
     </row>
     <row r="45">
@@ -6754,7 +6773,7 @@
         <v>43.0</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
     </row>
     <row r="46">
@@ -6762,7 +6781,7 @@
         <v>44.0</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>224</v>
+        <v>247</v>
       </c>
     </row>
     <row r="47">
@@ -6770,7 +6789,7 @@
         <v>45.0</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
     </row>
     <row r="48">
@@ -6778,7 +6797,7 @@
         <v>46.0</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>154</v>
+        <v>199</v>
       </c>
     </row>
     <row r="49">
@@ -6786,7 +6805,7 @@
         <v>47.0</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
     </row>
     <row r="50">
@@ -6794,7 +6813,7 @@
         <v>48.0</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
     </row>
     <row r="51">
@@ -6802,7 +6821,7 @@
         <v>49.0</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>67</v>
+        <v>53</v>
       </c>
     </row>
     <row r="52">
@@ -6810,7 +6829,7 @@
         <v>50.0</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
     </row>
     <row r="53">
@@ -6818,7 +6837,7 @@
         <v>51.0</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>167</v>
+        <v>206</v>
       </c>
     </row>
     <row r="54">
@@ -6826,7 +6845,7 @@
         <v>52.0</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>70</v>
+        <v>56</v>
       </c>
     </row>
     <row r="55">
@@ -6834,7 +6853,7 @@
         <v>53.0</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>73</v>
+        <v>57</v>
       </c>
     </row>
     <row r="56">
@@ -6842,7 +6861,7 @@
         <v>54.0</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
     </row>
     <row r="57">
@@ -6850,7 +6869,7 @@
         <v>55.0</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>179</v>
+        <v>212</v>
       </c>
     </row>
     <row r="58">
@@ -6858,7 +6877,7 @@
         <v>56.0</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>238</v>
+        <v>260</v>
       </c>
     </row>
     <row r="59">
@@ -6866,7 +6885,7 @@
         <v>57.0</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>240</v>
+        <v>261</v>
       </c>
     </row>
     <row r="60">
@@ -6874,7 +6893,7 @@
         <v>58.0</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
     </row>
     <row r="61">
@@ -6882,7 +6901,7 @@
         <v>59.0</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>78</v>
+        <v>63</v>
       </c>
     </row>
     <row r="62">
@@ -6890,7 +6909,7 @@
         <v>60.0</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>184</v>
+        <v>217</v>
       </c>
     </row>
     <row r="63">
@@ -6898,7 +6917,7 @@
         <v>61.0</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
     </row>
     <row r="64">
@@ -6906,7 +6925,7 @@
         <v>62.0</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>188</v>
+        <v>218</v>
       </c>
     </row>
     <row r="65">
@@ -6914,7 +6933,7 @@
         <v>63.0</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
     </row>
     <row r="66">
@@ -6922,7 +6941,7 @@
         <v>64.0</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>249</v>
+        <v>264</v>
       </c>
     </row>
     <row r="67">
@@ -6930,7 +6949,7 @@
         <v>65.0</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
     </row>
     <row r="68">
@@ -6938,7 +6957,7 @@
         <v>66.0</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
     </row>
     <row r="69">
@@ -6946,7 +6965,7 @@
         <v>67.0</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>251</v>
+        <v>268</v>
       </c>
     </row>
     <row r="70">
@@ -6954,7 +6973,7 @@
         <v>68.0</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>253</v>
+        <v>271</v>
       </c>
     </row>
     <row r="71">
@@ -6962,7 +6981,7 @@
         <v>69.0</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
     </row>
     <row r="72">
@@ -6970,7 +6989,7 @@
         <v>70.0</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>256</v>
+        <v>274</v>
       </c>
     </row>
     <row r="73">
@@ -6978,7 +6997,7 @@
         <v>71.0</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>258</v>
+        <v>276</v>
       </c>
     </row>
     <row r="74">
@@ -6986,7 +7005,7 @@
         <v>72.0</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>196</v>
+        <v>222</v>
       </c>
     </row>
     <row r="75">
@@ -6994,7 +7013,7 @@
         <v>73.0</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>260</v>
+        <v>278</v>
       </c>
     </row>
     <row r="76">
@@ -7002,7 +7021,7 @@
         <v>74.0</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>262</v>
+        <v>279</v>
       </c>
     </row>
     <row r="77">
@@ -7010,7 +7029,7 @@
         <v>75.0</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>48</v>
+        <v>64</v>
       </c>
     </row>
     <row r="78">
@@ -7018,7 +7037,7 @@
         <v>76.0</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>198</v>
+        <v>224</v>
       </c>
     </row>
     <row r="79">
@@ -7026,7 +7045,7 @@
         <v>77.0</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>267</v>
+        <v>280</v>
       </c>
     </row>
     <row r="80">
@@ -7034,7 +7053,7 @@
         <v>78.0</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
     </row>
     <row r="81">
@@ -7042,7 +7061,7 @@
         <v>79.0</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
     </row>
     <row r="82">
@@ -7050,7 +7069,7 @@
         <v>80.0</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
     </row>
     <row r="83">
@@ -7058,7 +7077,7 @@
         <v>81.0</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
     </row>
     <row r="84">
@@ -7066,7 +7085,7 @@
         <v>82.0</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
     </row>
     <row r="85">
@@ -7074,7 +7093,7 @@
         <v>83.0</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
     </row>
     <row r="86">
@@ -7082,7 +7101,7 @@
         <v>84.0</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
     </row>
     <row r="87">
@@ -7090,7 +7109,7 @@
         <v>85.0</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
     </row>
     <row r="88">
@@ -7098,7 +7117,7 @@
         <v>86.0</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
     </row>
     <row r="89">
@@ -7106,7 +7125,7 @@
         <v>87.0</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="90">
@@ -7114,7 +7133,7 @@
         <v>88.0</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
     </row>
     <row r="91">
@@ -7122,7 +7141,7 @@
         <v>89.0</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
     </row>
     <row r="92">
@@ -7130,7 +7149,7 @@
         <v>90.0</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
     </row>
     <row r="93">
@@ -7138,7 +7157,7 @@
         <v>91.0</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
     </row>
     <row r="94">
@@ -7146,7 +7165,7 @@
         <v>92.0</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>218</v>
+        <v>259</v>
       </c>
     </row>
     <row r="95">
@@ -7154,7 +7173,7 @@
         <v>93.0</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
     </row>
     <row r="96">
@@ -7162,7 +7181,7 @@
         <v>94.0</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="97">
@@ -7170,7 +7189,7 @@
         <v>95.0</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
     </row>
     <row r="98">
@@ -7178,7 +7197,7 @@
         <v>96.0</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
     </row>
     <row r="99">
@@ -7186,7 +7205,7 @@
         <v>97.0</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
     </row>
     <row r="100">
@@ -7194,7 +7213,7 @@
         <v>98.0</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>62</v>
+        <v>78</v>
       </c>
     </row>
     <row r="101">
@@ -7202,7 +7221,7 @@
         <v>99.0</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>226</v>
+        <v>262</v>
       </c>
     </row>
     <row r="102">
@@ -7210,7 +7229,7 @@
         <v>100.0</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
     </row>
     <row r="103">
@@ -7218,7 +7237,7 @@
         <v>101.0</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
     </row>
     <row r="104">
@@ -7226,7 +7245,7 @@
         <v>102.0</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
     </row>
     <row r="105">
@@ -7234,7 +7253,7 @@
         <v>103.0</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="106">
@@ -7250,7 +7269,7 @@
         <v>105.0</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
     </row>
     <row r="108">
@@ -7258,7 +7277,7 @@
         <v>106.0</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
     </row>
     <row r="109">
@@ -7266,7 +7285,7 @@
         <v>107.0</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
     </row>
     <row r="110">
@@ -7274,7 +7293,7 @@
         <v>108.0</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
     </row>
     <row r="111">
@@ -7298,7 +7317,7 @@
         <v>111.0</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
     </row>
     <row r="114">
@@ -7306,7 +7325,7 @@
         <v>112.0</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>234</v>
+        <v>265</v>
       </c>
     </row>
     <row r="115">
@@ -7314,7 +7333,7 @@
         <v>113.0</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
     </row>
     <row r="116">
@@ -7322,7 +7341,7 @@
         <v>114.0</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>241</v>
+        <v>269</v>
       </c>
     </row>
     <row r="117">
@@ -7330,7 +7349,7 @@
         <v>115.0</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
     </row>
     <row r="118">
@@ -7338,7 +7357,7 @@
         <v>116.0</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
     </row>
     <row r="119">
@@ -7346,7 +7365,7 @@
         <v>117.0</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
     </row>
     <row r="120">
@@ -7354,7 +7373,7 @@
         <v>118.0</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>245</v>
+        <v>275</v>
       </c>
     </row>
     <row r="121">
@@ -7362,7 +7381,7 @@
         <v>119.0</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
     </row>
     <row r="122">
@@ -7370,7 +7389,7 @@
         <v>120.0</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
     </row>
     <row r="123">
@@ -7378,7 +7397,7 @@
         <v>121.0</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
     </row>
     <row r="124">
@@ -7386,7 +7405,7 @@
         <v>122.0</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="125">
@@ -7394,7 +7413,7 @@
         <v>123.0</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
     </row>
     <row r="126">
@@ -7402,7 +7421,7 @@
         <v>124.0</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>124</v>
+        <v>110</v>
       </c>
     </row>
     <row r="127">
@@ -7410,7 +7429,7 @@
         <v>125.0</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="128">
@@ -7418,7 +7437,7 @@
         <v>126.0</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
     </row>
     <row r="129">
@@ -7426,7 +7445,7 @@
         <v>127.0</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="130">
@@ -7434,7 +7453,7 @@
         <v>128.0</v>
       </c>
       <c r="B130" s="3" t="s">
-        <v>128</v>
+        <v>111</v>
       </c>
     </row>
     <row r="131">
@@ -7442,7 +7461,7 @@
         <v>129.0</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
     </row>
     <row r="132">
@@ -7450,7 +7469,7 @@
         <v>130.0</v>
       </c>
       <c r="B132" s="3" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
     </row>
     <row r="133">
@@ -7458,7 +7477,7 @@
         <v>131.0</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
     </row>
     <row r="134">
@@ -7466,7 +7485,7 @@
         <v>132.0</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="135">
@@ -7474,7 +7493,7 @@
         <v>133.0</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>131</v>
+        <v>112</v>
       </c>
     </row>
     <row r="136">
@@ -7482,7 +7501,7 @@
         <v>134.0</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>134</v>
+        <v>113</v>
       </c>
     </row>
     <row r="137">
@@ -7490,7 +7509,7 @@
         <v>135.0</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
     </row>
     <row r="138">
@@ -7498,7 +7517,7 @@
         <v>136.0</v>
       </c>
       <c r="B138" s="3" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
     </row>
     <row r="139">
@@ -7506,7 +7525,7 @@
         <v>137.0</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>135</v>
+        <v>114</v>
       </c>
     </row>
     <row r="140">
@@ -7514,7 +7533,7 @@
         <v>138.0</v>
       </c>
       <c r="B140" s="3" t="s">
-        <v>136</v>
+        <v>115</v>
       </c>
     </row>
     <row r="141">
@@ -7522,7 +7541,7 @@
         <v>139.0</v>
       </c>
       <c r="B141" s="3" t="s">
-        <v>139</v>
+        <v>116</v>
       </c>
     </row>
     <row r="142">
@@ -7530,7 +7549,7 @@
         <v>140.0</v>
       </c>
       <c r="B142" s="3" t="s">
-        <v>140</v>
+        <v>117</v>
       </c>
     </row>
     <row r="143">
@@ -7538,7 +7557,7 @@
         <v>141.0</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>142</v>
+        <v>118</v>
       </c>
     </row>
     <row r="144">
@@ -7546,7 +7565,7 @@
         <v>142.0</v>
       </c>
       <c r="B144" s="3" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="145">
@@ -7562,7 +7581,7 @@
         <v>144.0</v>
       </c>
       <c r="B146" s="3" t="s">
-        <v>266</v>
+        <v>285</v>
       </c>
     </row>
     <row r="147">
@@ -7586,7 +7605,7 @@
         <v>147.0</v>
       </c>
       <c r="B149" s="3" t="s">
-        <v>144</v>
+        <v>119</v>
       </c>
     </row>
     <row r="150">
@@ -7594,7 +7613,7 @@
         <v>148.0</v>
       </c>
       <c r="B150" s="3" t="s">
-        <v>146</v>
+        <v>120</v>
       </c>
     </row>
     <row r="151">
@@ -7602,7 +7621,7 @@
         <v>149.0</v>
       </c>
       <c r="B151" s="3" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="152">
@@ -7610,7 +7629,7 @@
         <v>150.0</v>
       </c>
       <c r="B152" s="3" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="153">
@@ -7618,7 +7637,7 @@
         <v>151.0</v>
       </c>
       <c r="B153" s="3" t="s">
-        <v>270</v>
+        <v>286</v>
       </c>
     </row>
     <row r="154">
@@ -7634,7 +7653,7 @@
         <v>153.0</v>
       </c>
       <c r="B155" s="3" t="s">
-        <v>148</v>
+        <v>121</v>
       </c>
     </row>
     <row r="156">
@@ -7642,7 +7661,7 @@
         <v>154.0</v>
       </c>
       <c r="B156" s="3" t="s">
-        <v>150</v>
+        <v>122</v>
       </c>
     </row>
     <row r="157">
@@ -7658,7 +7677,7 @@
         <v>156.0</v>
       </c>
       <c r="B158" s="3" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
     </row>
     <row r="159">
@@ -7666,7 +7685,7 @@
         <v>157.0</v>
       </c>
       <c r="B159" s="3" t="s">
-        <v>151</v>
+        <v>123</v>
       </c>
     </row>
     <row r="160">
@@ -7674,7 +7693,7 @@
         <v>158.0</v>
       </c>
       <c r="B160" s="3" t="s">
-        <v>278</v>
+        <v>292</v>
       </c>
     </row>
     <row r="161">
@@ -7682,7 +7701,7 @@
         <v>159.0</v>
       </c>
       <c r="B161" s="3" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
     </row>
     <row r="162">
@@ -7714,7 +7733,7 @@
         <v>163.0</v>
       </c>
       <c r="B165" s="3" t="s">
-        <v>159</v>
+        <v>124</v>
       </c>
     </row>
     <row r="166">
@@ -7722,7 +7741,7 @@
         <v>164.0</v>
       </c>
       <c r="B166" s="3" t="s">
-        <v>162</v>
+        <v>125</v>
       </c>
     </row>
     <row r="167">
@@ -7730,7 +7749,7 @@
         <v>165.0</v>
       </c>
       <c r="B167" s="3" t="s">
-        <v>283</v>
+        <v>300</v>
       </c>
     </row>
     <row r="168">
@@ -7738,7 +7757,7 @@
         <v>166.0</v>
       </c>
       <c r="B168" s="3" t="s">
-        <v>285</v>
+        <v>303</v>
       </c>
     </row>
     <row r="169">
@@ -7746,7 +7765,7 @@
         <v>167.0</v>
       </c>
       <c r="B169" s="3" t="s">
-        <v>27</v>
+        <v>48</v>
       </c>
     </row>
     <row r="170">
@@ -7754,7 +7773,7 @@
         <v>168.0</v>
       </c>
       <c r="B170" s="3" t="s">
-        <v>165</v>
+        <v>126</v>
       </c>
     </row>
     <row r="171">
@@ -7762,7 +7781,7 @@
         <v>169.0</v>
       </c>
       <c r="B171" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="172">
@@ -7770,7 +7789,7 @@
         <v>170.0</v>
       </c>
       <c r="B172" s="3" t="s">
-        <v>169</v>
+        <v>127</v>
       </c>
     </row>
     <row r="173">
@@ -7778,7 +7797,7 @@
         <v>171.0</v>
       </c>
       <c r="B173" s="3" t="s">
-        <v>171</v>
+        <v>128</v>
       </c>
     </row>
     <row r="174">
@@ -7786,7 +7805,7 @@
         <v>172.0</v>
       </c>
       <c r="B174" s="3" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
     </row>
     <row r="175">
@@ -7794,7 +7813,7 @@
         <v>173.0</v>
       </c>
       <c r="B175" s="3" t="s">
-        <v>296</v>
+        <v>311</v>
       </c>
     </row>
     <row r="176">
@@ -7802,7 +7821,7 @@
         <v>174.0</v>
       </c>
       <c r="B176" s="3" t="s">
-        <v>297</v>
+        <v>313</v>
       </c>
     </row>
     <row r="177">
@@ -7810,7 +7829,7 @@
         <v>175.0</v>
       </c>
       <c r="B177" s="3" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
     </row>
     <row r="178">
@@ -7818,7 +7837,7 @@
         <v>176.0</v>
       </c>
       <c r="B178" s="3" t="s">
-        <v>176</v>
+        <v>129</v>
       </c>
     </row>
     <row r="179">
@@ -7826,7 +7845,7 @@
         <v>177.0</v>
       </c>
       <c r="B179" s="3" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="180">
@@ -7834,7 +7853,7 @@
         <v>178.0</v>
       </c>
       <c r="B180" s="3" t="s">
-        <v>180</v>
+        <v>130</v>
       </c>
     </row>
     <row r="181">
@@ -7842,7 +7861,7 @@
         <v>179.0</v>
       </c>
       <c r="B181" s="3" t="s">
-        <v>182</v>
+        <v>131</v>
       </c>
     </row>
     <row r="182">
@@ -7850,7 +7869,7 @@
         <v>180.0</v>
       </c>
       <c r="B182" s="3" t="s">
-        <v>306</v>
+        <v>315</v>
       </c>
     </row>
     <row r="183">
@@ -7858,7 +7877,7 @@
         <v>181.0</v>
       </c>
       <c r="B183" s="3" t="s">
-        <v>309</v>
+        <v>316</v>
       </c>
     </row>
     <row r="184">
@@ -7866,7 +7885,7 @@
         <v>182.0</v>
       </c>
       <c r="B184" s="3" t="s">
-        <v>183</v>
+        <v>132</v>
       </c>
     </row>
     <row r="185">
@@ -7874,7 +7893,7 @@
         <v>183.0</v>
       </c>
       <c r="B185" s="3" t="s">
-        <v>185</v>
+        <v>133</v>
       </c>
     </row>
     <row r="186">
@@ -7890,7 +7909,7 @@
         <v>185.0</v>
       </c>
       <c r="B187" s="3" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="188">
@@ -7898,7 +7917,7 @@
         <v>186.0</v>
       </c>
       <c r="B188" s="3" t="s">
-        <v>187</v>
+        <v>134</v>
       </c>
     </row>
     <row r="189">
@@ -7906,7 +7925,7 @@
         <v>187.0</v>
       </c>
       <c r="B189" s="3" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="190">
@@ -7914,7 +7933,7 @@
         <v>188.0</v>
       </c>
       <c r="B190" s="3" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="191">
@@ -7922,7 +7941,7 @@
         <v>189.0</v>
       </c>
       <c r="B191" s="3" t="s">
-        <v>189</v>
+        <v>135</v>
       </c>
     </row>
     <row r="192">
@@ -7938,7 +7957,7 @@
         <v>191.0</v>
       </c>
       <c r="B193" s="3" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="194">
@@ -7946,7 +7965,7 @@
         <v>192.0</v>
       </c>
       <c r="B194" s="3" t="s">
-        <v>192</v>
+        <v>136</v>
       </c>
     </row>
     <row r="195">
@@ -7978,7 +7997,7 @@
         <v>196.0</v>
       </c>
       <c r="B198" s="3" t="s">
-        <v>54</v>
+        <v>70</v>
       </c>
     </row>
     <row r="199">
@@ -7986,7 +8005,7 @@
         <v>197.0</v>
       </c>
       <c r="B199" s="3" t="s">
-        <v>327</v>
+        <v>319</v>
       </c>
     </row>
     <row r="200">
@@ -7994,7 +8013,7 @@
         <v>198.0</v>
       </c>
       <c r="B200" s="3" t="s">
-        <v>193</v>
+        <v>137</v>
       </c>
     </row>
     <row r="201">
@@ -8002,7 +8021,7 @@
         <v>199.0</v>
       </c>
       <c r="B201" s="3" t="s">
-        <v>194</v>
+        <v>138</v>
       </c>
     </row>
     <row r="202">
@@ -8010,7 +8029,7 @@
         <v>200.0</v>
       </c>
       <c r="B202" s="3" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
     </row>
     <row r="203">
@@ -8018,7 +8037,7 @@
         <v>201.0</v>
       </c>
       <c r="B203" s="3" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
     </row>
     <row r="204">
@@ -8026,7 +8045,7 @@
         <v>202.0</v>
       </c>
       <c r="B204" s="3" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
     </row>
     <row r="205">
@@ -8034,7 +8053,7 @@
         <v>203.0</v>
       </c>
       <c r="B205" s="3" t="s">
-        <v>72</v>
+        <v>91</v>
       </c>
     </row>
     <row r="206">
@@ -8042,7 +8061,7 @@
         <v>204.0</v>
       </c>
       <c r="B206" s="3" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
     </row>
     <row r="207">
@@ -8050,7 +8069,7 @@
         <v>205.0</v>
       </c>
       <c r="B207" s="3" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
     </row>
     <row r="208">
@@ -8058,7 +8077,7 @@
         <v>206.0</v>
       </c>
       <c r="B208" s="3" t="s">
-        <v>335</v>
+        <v>328</v>
       </c>
     </row>
     <row r="209">
@@ -8066,7 +8085,7 @@
         <v>207.0</v>
       </c>
       <c r="B209" s="3" t="s">
-        <v>199</v>
+        <v>139</v>
       </c>
     </row>
     <row r="210">
@@ -8106,7 +8125,7 @@
         <v>212.0</v>
       </c>
       <c r="B214" s="3" t="s">
-        <v>201</v>
+        <v>140</v>
       </c>
     </row>
     <row r="215">
@@ -8114,7 +8133,7 @@
         <v>213.0</v>
       </c>
       <c r="B215" s="3" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="216">
@@ -8122,7 +8141,7 @@
         <v>214.0</v>
       </c>
       <c r="B216" s="3" t="s">
-        <v>204</v>
+        <v>141</v>
       </c>
     </row>
     <row r="217">
@@ -8146,7 +8165,7 @@
         <v>217.0</v>
       </c>
       <c r="B219" s="3" t="s">
-        <v>206</v>
+        <v>143</v>
       </c>
     </row>
     <row r="220">
@@ -8162,7 +8181,7 @@
         <v>219.0</v>
       </c>
       <c r="B221" s="3" t="s">
-        <v>207</v>
+        <v>144</v>
       </c>
     </row>
     <row r="222">
@@ -8170,7 +8189,7 @@
         <v>220.0</v>
       </c>
       <c r="B222" s="3" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
     </row>
     <row r="223">
@@ -8186,7 +8205,7 @@
         <v>222.0</v>
       </c>
       <c r="B224" s="3" t="s">
-        <v>209</v>
+        <v>145</v>
       </c>
     </row>
     <row r="225">
@@ -8194,7 +8213,7 @@
         <v>223.0</v>
       </c>
       <c r="B225" s="3" t="s">
-        <v>211</v>
+        <v>146</v>
       </c>
     </row>
     <row r="226">
@@ -8202,7 +8221,7 @@
         <v>224.0</v>
       </c>
       <c r="B226" s="3" t="s">
-        <v>212</v>
+        <v>147</v>
       </c>
     </row>
     <row r="227">
@@ -8210,7 +8229,7 @@
         <v>225.0</v>
       </c>
       <c r="B227" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="228">
@@ -8218,7 +8237,7 @@
         <v>226.0</v>
       </c>
       <c r="B228" s="3" t="s">
-        <v>213</v>
+        <v>148</v>
       </c>
     </row>
     <row r="229">
@@ -8226,7 +8245,7 @@
         <v>227.0</v>
       </c>
       <c r="B229" s="3" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="230">
@@ -8234,7 +8253,7 @@
         <v>228.0</v>
       </c>
       <c r="B230" s="3" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="231">
@@ -8242,7 +8261,7 @@
         <v>229.0</v>
       </c>
       <c r="B231" s="3" t="s">
-        <v>215</v>
+        <v>149</v>
       </c>
     </row>
     <row r="232">
@@ -8250,7 +8269,7 @@
         <v>230.0</v>
       </c>
       <c r="B232" s="3" t="s">
-        <v>217</v>
+        <v>150</v>
       </c>
     </row>
     <row r="233">
@@ -8258,7 +8277,7 @@
         <v>231.0</v>
       </c>
       <c r="B233" s="3" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
     </row>
     <row r="234">
@@ -8266,7 +8285,7 @@
         <v>232.0</v>
       </c>
       <c r="B234" s="3" t="s">
-        <v>220</v>
+        <v>151</v>
       </c>
     </row>
     <row r="235">
@@ -8274,7 +8293,7 @@
         <v>233.0</v>
       </c>
       <c r="B235" s="3" t="s">
-        <v>222</v>
+        <v>152</v>
       </c>
     </row>
     <row r="236">
@@ -8282,7 +8301,7 @@
         <v>234.0</v>
       </c>
       <c r="B236" s="3" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
     </row>
     <row r="237">
@@ -8290,7 +8309,7 @@
         <v>235.0</v>
       </c>
       <c r="B237" s="3" t="s">
-        <v>223</v>
+        <v>153</v>
       </c>
     </row>
     <row r="238">
@@ -8298,7 +8317,7 @@
         <v>236.0</v>
       </c>
       <c r="B238" s="3" t="s">
-        <v>225</v>
+        <v>154</v>
       </c>
     </row>
     <row r="239">
@@ -8306,7 +8325,7 @@
         <v>237.0</v>
       </c>
       <c r="B239" s="3" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
     </row>
     <row r="240">
@@ -8314,7 +8333,7 @@
         <v>238.0</v>
       </c>
       <c r="B240" s="3" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="241">
@@ -8322,7 +8341,7 @@
         <v>239.0</v>
       </c>
       <c r="B241" s="3" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
     </row>
     <row r="242">
@@ -8330,7 +8349,7 @@
         <v>240.0</v>
       </c>
       <c r="B242" s="3" t="s">
-        <v>227</v>
+        <v>155</v>
       </c>
     </row>
     <row r="243">
@@ -8338,7 +8357,7 @@
         <v>241.0</v>
       </c>
       <c r="B243" s="3" t="s">
-        <v>228</v>
+        <v>156</v>
       </c>
     </row>
     <row r="244">
@@ -8346,7 +8365,7 @@
         <v>242.0</v>
       </c>
       <c r="B244" s="3" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="245">
@@ -8354,7 +8373,7 @@
         <v>243.0</v>
       </c>
       <c r="B245" s="3" t="s">
-        <v>229</v>
+        <v>157</v>
       </c>
     </row>
     <row r="246">
@@ -8362,7 +8381,7 @@
         <v>244.0</v>
       </c>
       <c r="B246" s="3" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="247">
@@ -8370,7 +8389,7 @@
         <v>245.0</v>
       </c>
       <c r="B247" s="3" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="248">
@@ -8378,7 +8397,7 @@
         <v>246.0</v>
       </c>
       <c r="B248" s="3" t="s">
-        <v>230</v>
+        <v>159</v>
       </c>
     </row>
     <row r="249">
@@ -8386,7 +8405,7 @@
         <v>247.0</v>
       </c>
       <c r="B249" s="3" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="250">
@@ -8394,7 +8413,7 @@
         <v>248.0</v>
       </c>
       <c r="B250" s="3" t="s">
-        <v>231</v>
+        <v>160</v>
       </c>
     </row>
     <row r="251">
@@ -8402,7 +8421,7 @@
         <v>249.0</v>
       </c>
       <c r="B251" s="3" t="s">
-        <v>232</v>
+        <v>161</v>
       </c>
     </row>
     <row r="252">
@@ -8418,7 +8437,7 @@
         <v>251.0</v>
       </c>
       <c r="B253" s="3" t="s">
-        <v>233</v>
+        <v>163</v>
       </c>
     </row>
     <row r="254">
@@ -8434,7 +8453,7 @@
         <v>253.0</v>
       </c>
       <c r="B255" s="3" t="s">
-        <v>235</v>
+        <v>164</v>
       </c>
     </row>
     <row r="256">
@@ -8450,7 +8469,7 @@
         <v>255.0</v>
       </c>
       <c r="B257" s="3" t="s">
-        <v>236</v>
+        <v>165</v>
       </c>
     </row>
     <row r="258">
@@ -8474,7 +8493,7 @@
         <v>258.0</v>
       </c>
       <c r="B260" s="3" t="s">
-        <v>237</v>
+        <v>166</v>
       </c>
     </row>
     <row r="261">
@@ -8482,7 +8501,7 @@
         <v>259.0</v>
       </c>
       <c r="B261" s="3" t="s">
-        <v>239</v>
+        <v>168</v>
       </c>
     </row>
     <row r="262">
@@ -8490,7 +8509,7 @@
         <v>260.0</v>
       </c>
       <c r="B262" s="3" t="s">
-        <v>242</v>
+        <v>169</v>
       </c>
     </row>
     <row r="263">
@@ -8514,7 +8533,7 @@
         <v>263.0</v>
       </c>
       <c r="B265" s="3" t="s">
-        <v>34</v>
+        <v>52</v>
       </c>
     </row>
     <row r="266">
@@ -8538,7 +8557,7 @@
         <v>266.0</v>
       </c>
       <c r="B268" s="3" t="s">
-        <v>243</v>
+        <v>171</v>
       </c>
     </row>
     <row r="269">
@@ -8554,7 +8573,7 @@
         <v>268.0</v>
       </c>
       <c r="B270" s="3" t="s">
-        <v>244</v>
+        <v>173</v>
       </c>
     </row>
     <row r="271">
@@ -8562,7 +8581,7 @@
         <v>269.0</v>
       </c>
       <c r="B271" s="3" t="s">
-        <v>246</v>
+        <v>174</v>
       </c>
     </row>
     <row r="272">
@@ -8570,7 +8589,7 @@
         <v>270.0</v>
       </c>
       <c r="B272" s="3" t="s">
-        <v>247</v>
+        <v>175</v>
       </c>
     </row>
     <row r="273">
@@ -8578,7 +8597,7 @@
         <v>271.0</v>
       </c>
       <c r="B273" s="3" t="s">
-        <v>248</v>
+        <v>176</v>
       </c>
     </row>
     <row r="274">
@@ -8586,7 +8605,7 @@
         <v>272.0</v>
       </c>
       <c r="B274" s="3" t="s">
-        <v>12</v>
+        <v>37</v>
       </c>
     </row>
     <row r="275">
@@ -8602,7 +8621,7 @@
         <v>274.0</v>
       </c>
       <c r="B276" s="3" t="s">
-        <v>250</v>
+        <v>178</v>
       </c>
     </row>
     <row r="277">
@@ -8610,7 +8629,7 @@
         <v>275.0</v>
       </c>
       <c r="B277" s="3" t="s">
-        <v>74</v>
+        <v>93</v>
       </c>
     </row>
     <row r="278">
@@ -8618,7 +8637,7 @@
         <v>276.0</v>
       </c>
       <c r="B278" s="3" t="s">
-        <v>252</v>
+        <v>181</v>
       </c>
     </row>
     <row r="279">
@@ -8626,7 +8645,7 @@
         <v>277.0</v>
       </c>
       <c r="B279" s="3" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="280">
@@ -8658,7 +8677,7 @@
         <v>281.0</v>
       </c>
       <c r="B283" s="3" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="284">
@@ -8666,7 +8685,7 @@
         <v>282.0</v>
       </c>
       <c r="B284" s="3" t="s">
-        <v>254</v>
+        <v>183</v>
       </c>
     </row>
     <row r="285">
@@ -8674,7 +8693,7 @@
         <v>283.0</v>
       </c>
       <c r="B285" s="3" t="s">
-        <v>255</v>
+        <v>185</v>
       </c>
     </row>
     <row r="286">
@@ -8706,7 +8725,7 @@
         <v>287.0</v>
       </c>
       <c r="B289" s="3" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="290">
@@ -8714,7 +8733,7 @@
         <v>288.0</v>
       </c>
       <c r="B290" s="3" t="s">
-        <v>257</v>
+        <v>187</v>
       </c>
     </row>
     <row r="291">
@@ -8722,7 +8741,7 @@
         <v>289.0</v>
       </c>
       <c r="B291" s="3" t="s">
-        <v>79</v>
+        <v>97</v>
       </c>
     </row>
     <row r="292">
@@ -8730,7 +8749,7 @@
         <v>290.0</v>
       </c>
       <c r="B292" s="3" t="s">
-        <v>259</v>
+        <v>188</v>
       </c>
     </row>
     <row r="293">
@@ -8738,7 +8757,7 @@
         <v>291.0</v>
       </c>
       <c r="B293" s="3" t="s">
-        <v>83</v>
+        <v>101</v>
       </c>
     </row>
     <row r="294">
@@ -8770,7 +8789,7 @@
         <v>295.0</v>
       </c>
       <c r="B297" s="3" t="s">
-        <v>261</v>
+        <v>189</v>
       </c>
     </row>
     <row r="298">
@@ -8778,7 +8797,7 @@
         <v>296.0</v>
       </c>
       <c r="B298" s="3" t="s">
-        <v>263</v>
+        <v>190</v>
       </c>
     </row>
     <row r="299">
@@ -8802,7 +8821,7 @@
         <v>299.0</v>
       </c>
       <c r="B301" s="3" t="s">
-        <v>264</v>
+        <v>192</v>
       </c>
     </row>
     <row r="302">
@@ -8810,7 +8829,7 @@
         <v>300.0</v>
       </c>
       <c r="B302" s="3" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
     </row>
     <row r="303">
@@ -8818,7 +8837,7 @@
         <v>301.0</v>
       </c>
       <c r="B303" s="3" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="304">
@@ -8826,7 +8845,7 @@
         <v>302.0</v>
       </c>
       <c r="B304" s="3" t="s">
-        <v>265</v>
+        <v>194</v>
       </c>
     </row>
     <row r="305">
@@ -8834,7 +8853,7 @@
         <v>303.0</v>
       </c>
       <c r="B305" s="3" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
     </row>
     <row r="306">
@@ -8842,7 +8861,7 @@
         <v>304.0</v>
       </c>
       <c r="B306" s="3" t="s">
-        <v>268</v>
+        <v>196</v>
       </c>
     </row>
     <row r="307">
@@ -8850,7 +8869,7 @@
         <v>305.0</v>
       </c>
       <c r="B307" s="3" t="s">
-        <v>269</v>
+        <v>197</v>
       </c>
     </row>
     <row r="308">
@@ -8858,7 +8877,7 @@
         <v>306.0</v>
       </c>
       <c r="B308" s="3" t="s">
-        <v>271</v>
+        <v>198</v>
       </c>
     </row>
     <row r="309">
@@ -8866,7 +8885,7 @@
         <v>307.0</v>
       </c>
       <c r="B309" s="3" t="s">
-        <v>273</v>
+        <v>200</v>
       </c>
     </row>
     <row r="310">
@@ -8874,7 +8893,7 @@
         <v>308.0</v>
       </c>
       <c r="B310" s="3" t="s">
-        <v>274</v>
+        <v>201</v>
       </c>
     </row>
     <row r="311">
@@ -8890,7 +8909,7 @@
         <v>310.0</v>
       </c>
       <c r="B312" s="3" t="s">
-        <v>275</v>
+        <v>202</v>
       </c>
     </row>
     <row r="313">
@@ -8906,7 +8925,7 @@
         <v>312.0</v>
       </c>
       <c r="B314" s="3" t="s">
-        <v>277</v>
+        <v>204</v>
       </c>
     </row>
     <row r="315">
@@ -8922,7 +8941,7 @@
         <v>314.0</v>
       </c>
       <c r="B316" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="317">
@@ -8954,7 +8973,7 @@
         <v>318.0</v>
       </c>
       <c r="B320" s="3" t="s">
-        <v>280</v>
+        <v>205</v>
       </c>
     </row>
     <row r="321">
@@ -8986,7 +9005,7 @@
         <v>322.0</v>
       </c>
       <c r="B324" s="3" t="s">
-        <v>281</v>
+        <v>207</v>
       </c>
     </row>
     <row r="325">
@@ -9002,7 +9021,7 @@
         <v>324.0</v>
       </c>
       <c r="B326" s="3" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
     </row>
     <row r="327">
@@ -9018,7 +9037,7 @@
         <v>326.0</v>
       </c>
       <c r="B328" s="3" t="s">
-        <v>282</v>
+        <v>208</v>
       </c>
     </row>
     <row r="329">
@@ -9034,7 +9053,7 @@
         <v>328.0</v>
       </c>
       <c r="B330" s="3" t="s">
-        <v>284</v>
+        <v>209</v>
       </c>
     </row>
     <row r="331">
@@ -9042,7 +9061,7 @@
         <v>329.0</v>
       </c>
       <c r="B331" s="3" t="s">
-        <v>286</v>
+        <v>211</v>
       </c>
     </row>
     <row r="332">
@@ -9050,7 +9069,7 @@
         <v>330.0</v>
       </c>
       <c r="B332" s="3" t="s">
-        <v>287</v>
+        <v>213</v>
       </c>
     </row>
     <row r="333">
@@ -9074,7 +9093,7 @@
         <v>333.0</v>
       </c>
       <c r="B335" s="3" t="s">
-        <v>288</v>
+        <v>214</v>
       </c>
     </row>
     <row r="336">
@@ -9082,7 +9101,7 @@
         <v>334.0</v>
       </c>
       <c r="B336" s="3" t="s">
-        <v>290</v>
+        <v>215</v>
       </c>
     </row>
     <row r="337">
@@ -9122,7 +9141,7 @@
         <v>339.0</v>
       </c>
       <c r="B341" s="3" t="s">
-        <v>291</v>
+        <v>220</v>
       </c>
     </row>
     <row r="342">
@@ -9130,7 +9149,7 @@
         <v>340.0</v>
       </c>
       <c r="B342" s="3" t="s">
-        <v>293</v>
+        <v>221</v>
       </c>
     </row>
     <row r="343">
@@ -9138,7 +9157,7 @@
         <v>341.0</v>
       </c>
       <c r="B343" s="3" t="s">
-        <v>295</v>
+        <v>223</v>
       </c>
     </row>
     <row r="344">
@@ -9154,7 +9173,7 @@
         <v>343.0</v>
       </c>
       <c r="B345" s="3" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
     </row>
     <row r="346">
@@ -9162,7 +9181,7 @@
         <v>344.0</v>
       </c>
       <c r="B346" s="3" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
     </row>
     <row r="347">
@@ -9170,7 +9189,7 @@
         <v>345.0</v>
       </c>
       <c r="B347" s="3" t="s">
-        <v>299</v>
+        <v>226</v>
       </c>
     </row>
     <row r="348">
@@ -9186,7 +9205,7 @@
         <v>347.0</v>
       </c>
       <c r="B349" s="3" t="s">
-        <v>300</v>
+        <v>227</v>
       </c>
     </row>
     <row r="350">
@@ -9194,7 +9213,7 @@
         <v>348.0</v>
       </c>
       <c r="B350" s="3" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="351">
@@ -9202,7 +9221,7 @@
         <v>349.0</v>
       </c>
       <c r="B351" s="3" t="s">
-        <v>303</v>
+        <v>229</v>
       </c>
     </row>
     <row r="352">
@@ -9226,7 +9245,7 @@
         <v>352.0</v>
       </c>
       <c r="B354" s="3" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
     </row>
     <row r="355">
@@ -9234,7 +9253,7 @@
         <v>353.0</v>
       </c>
       <c r="B355" s="3" t="s">
-        <v>46</v>
+        <v>62</v>
       </c>
     </row>
     <row r="356">
@@ -9242,7 +9261,7 @@
         <v>354.0</v>
       </c>
       <c r="B356" s="3" t="s">
-        <v>305</v>
+        <v>233</v>
       </c>
     </row>
     <row r="357">
@@ -9250,7 +9269,7 @@
         <v>355.0</v>
       </c>
       <c r="B357" s="3" t="s">
-        <v>307</v>
+        <v>234</v>
       </c>
     </row>
     <row r="358">
@@ -9258,7 +9277,7 @@
         <v>356.0</v>
       </c>
       <c r="B358" s="3" t="s">
-        <v>308</v>
+        <v>237</v>
       </c>
     </row>
     <row r="359">
@@ -9266,7 +9285,7 @@
         <v>357.0</v>
       </c>
       <c r="B359" s="3" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="360">
@@ -9274,7 +9293,7 @@
         <v>358.0</v>
       </c>
       <c r="B360" s="3" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
     </row>
     <row r="361">
@@ -9290,7 +9309,7 @@
         <v>360.0</v>
       </c>
       <c r="B362" s="3" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
     </row>
     <row r="363">
@@ -9314,7 +9333,7 @@
         <v>363.0</v>
       </c>
       <c r="B365" s="3" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="366">
@@ -9330,7 +9349,7 @@
         <v>365.0</v>
       </c>
       <c r="B367" s="3" t="s">
-        <v>311</v>
+        <v>241</v>
       </c>
     </row>
     <row r="368">
@@ -9338,7 +9357,7 @@
         <v>366.0</v>
       </c>
       <c r="B368" s="3" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="369">
@@ -9346,7 +9365,7 @@
         <v>367.0</v>
       </c>
       <c r="B369" s="3" t="s">
-        <v>313</v>
+        <v>244</v>
       </c>
     </row>
     <row r="370">
@@ -9362,7 +9381,7 @@
         <v>369.0</v>
       </c>
       <c r="B371" s="3" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="372">
@@ -9370,7 +9389,7 @@
         <v>370.0</v>
       </c>
       <c r="B372" s="3" t="s">
-        <v>314</v>
+        <v>246</v>
       </c>
     </row>
     <row r="373">
@@ -9378,7 +9397,7 @@
         <v>371.0</v>
       </c>
       <c r="B373" s="3" t="s">
-        <v>315</v>
+        <v>248</v>
       </c>
     </row>
     <row r="374">
@@ -9386,7 +9405,7 @@
         <v>372.0</v>
       </c>
       <c r="B374" s="3" t="s">
-        <v>316</v>
+        <v>250</v>
       </c>
     </row>
     <row r="375">
@@ -9402,7 +9421,7 @@
         <v>374.0</v>
       </c>
       <c r="B376" s="3" t="s">
-        <v>318</v>
+        <v>251</v>
       </c>
     </row>
     <row r="377">
@@ -9410,7 +9429,7 @@
         <v>375.0</v>
       </c>
       <c r="B377" s="3" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
     </row>
     <row r="378">
@@ -9434,7 +9453,7 @@
         <v>378.0</v>
       </c>
       <c r="B380" s="3" t="s">
-        <v>320</v>
+        <v>252</v>
       </c>
     </row>
     <row r="381">
@@ -9442,7 +9461,7 @@
         <v>379.0</v>
       </c>
       <c r="B381" s="3" t="s">
-        <v>321</v>
+        <v>253</v>
       </c>
     </row>
     <row r="382">
@@ -9458,7 +9477,7 @@
         <v>381.0</v>
       </c>
       <c r="B383" s="3" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
     <row r="384">
@@ -9466,7 +9485,7 @@
         <v>382.0</v>
       </c>
       <c r="B384" s="3" t="s">
-        <v>322</v>
+        <v>255</v>
       </c>
     </row>
     <row r="385">
@@ -9474,7 +9493,7 @@
         <v>383.0</v>
       </c>
       <c r="B385" s="3" t="s">
-        <v>323</v>
+        <v>256</v>
       </c>
     </row>
     <row r="386">
@@ -9482,7 +9501,7 @@
         <v>384.0</v>
       </c>
       <c r="B386" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="387">
@@ -9490,7 +9509,7 @@
         <v>385.0</v>
       </c>
       <c r="B387" s="3" t="s">
-        <v>325</v>
+        <v>257</v>
       </c>
     </row>
     <row r="388">
@@ -9498,7 +9517,7 @@
         <v>386.0</v>
       </c>
       <c r="B388" s="3" t="s">
-        <v>326</v>
+        <v>258</v>
       </c>
     </row>
     <row r="389">
